--- a/Rental Final Table/LetzRyd_Rental_Master_Architecture_Complete.xlsx
+++ b/Rental Final Table/LetzRyd_Rental_Master_Architecture_Complete.xlsx
@@ -767,7 +767,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>public.rental_fee_rules — Daily indemnity insurance (Standard ₹30/day; Mumbai ₹0; Hyundai Xcent retired fleet ₹0; Waived partners ₹0). Net Daily Rent = Applied Rent + Applied Indemnity.</t>
+          <t>public.rental_fee_rules — Standardized daily indemnity insurance (Standard ₹30/day across all cities: Bangalore, Hyderabad, Mumbai; Hyundai Xcent retired fleet ₹0; Waived partners ₹0). Net Daily Rent = Applied Rent + Applied Indemnity.</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -815,7 +815,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="63" customWidth="1" min="7" max="7"/>
+    <col width="65" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
@@ -830,7 +830,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rules governing daily vehicle indemnity fees, model-specific waivers, and custom fee schedules (including Mumbai standard waiver).</t>
+          <t>Rules governing daily vehicle indemnity fees, model-specific waivers, and custom fee schedules.</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="B4" s="30" t="inlineStr">
         <is>
-          <t>fee_rule_id (SERIAL INT - Clean 1 to 7)</t>
+          <t>fee_rule_id (SERIAL INT - Clean 1 to 6)</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>1 row per fee policy or exemption rule (7 active rules)</t>
+          <t>1 row per fee policy or exemption rule (6 active rules)</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Resolves daily indemnity fee: Standard ₹30/day; Mumbai ₹0 (waiver); Xcent ₹0; Waived partners ₹0.</t>
+          <t>Resolves daily indemnity fee: Standard ₹30/day across all cities (Bangalore, Hyderabad, Mumbai); Xcent ₹0; Waived partners ₹0.</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>Standard daily indemnity across all cities</t>
+          <t>Standard daily indemnity across all cities (Bangalore, Hyderabad, Mumbai)</t>
         </is>
       </c>
       <c r="H11" s="33" t="n">
@@ -1162,43 +1162,6 @@
         <v>46023</v>
       </c>
       <c r="I16" s="34" t="n">
-        <v>2958465</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="37" t="n">
-        <v>7</v>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Mumbai</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="D17" s="9" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>Mumbai standard indemnity waiver (fee included in base rent)</t>
-        </is>
-      </c>
-      <c r="H17" s="33" t="n">
-        <v>46023</v>
-      </c>
-      <c r="I17" s="33" t="n">
         <v>2958465</v>
       </c>
     </row>
@@ -19865,7 +19828,7 @@
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -20491,8 +20454,8 @@
       <c r="G14" s="24" t="inlineStr">
         <is>
           <t>1. Calculates total weekly Uber trips.
-2. Matches into 6 discrete trip milestone tiers.
-3. Applies net rent (In Mumbai, base rent includes indemnity; standard fee is ₹0).</t>
+2. Matches into 6 discrete trip milestone tiers in rental_rate_slabs.
+3. Adds standard ₹30/day indemnity fee from rental_fee_rules.</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -20507,12 +20470,12 @@
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>₹0.00/day (Built into base)</t>
+          <t>₹30.00/day</t>
         </is>
       </c>
       <c r="J14" s="22" t="inlineStr">
         <is>
-          <t>Mumbai driver reaches 112 trips in the week. He enters the 110-124 slab (₹569/day). For 7 billable days, Total Rent = 7 × ₹569 = ₹3,983.</t>
+          <t>Mumbai driver reaches 112 trips in the week. He enters the 110-124 slab (₹569/day). Net rent = ₹569 + ₹30 = ₹599/day. For 7 billable days, Total Rent = 7 × ₹599 = ₹4,193.</t>
         </is>
       </c>
     </row>
@@ -20550,7 +20513,7 @@
       <c r="G15" s="21" t="inlineStr">
         <is>
           <t>1. Applies standard base rent of ₹1,100/day.
-2. Adds ₹30/day indemnity fee.
+2. Adds standard ₹30/day indemnity fee.
 3. Total net daily rent = ₹1,130/day.</t>
         </is>
       </c>
@@ -20598,28 +20561,28 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>Fixed-rate contract permitting dual-application driving.</t>
+          <t>Fixed-rate contract permitting dual-application driving with full company insurance cover.</t>
         </is>
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
           <t>1. Applies flat rate ₹1,050/day.
-2. Fee is ₹0/day.</t>
+2. Adds standard ₹30/day indemnity fee.</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
         <is>
-          <t>• Flat ₹1,050/day</t>
+          <t>• Flat ₹1,050/day base rent</t>
         </is>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>₹0.00/day</t>
+          <t>₹30.00/day</t>
         </is>
       </c>
       <c r="J16" s="22" t="inlineStr">
         <is>
-          <t>Driver operating across both platforms is billed 7 × ₹1,050 = ₹7,350.</t>
+          <t>Driver operating across both platforms is billed 7 × (1,050 + 30) = ₹7,560.</t>
         </is>
       </c>
     </row>
@@ -20657,24 +20620,24 @@
       <c r="G17" s="21" t="inlineStr">
         <is>
           <t>1. Fetches model baseline from rental_model_baselines.
-2. Applies city baseline rate.</t>
+2. Adds standard ₹30/day indemnity fee.</t>
         </is>
       </c>
       <c r="H17" s="19" t="inlineStr">
         <is>
-          <t>• WagonR: ₹970/day
-• Dzire / Aura: ₹1,100/day
-• Tigor EV: ₹1,300/day</t>
+          <t>• WagonR: ₹970 + ₹30 = ₹1,000/day
+• Dzire / Aura: ₹1,100 + ₹30 = ₹1,130/day
+• Tigor EV: ₹1,300 + ₹30 = ₹1,330/day</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>₹0.00/day</t>
+          <t>₹30.00/day</t>
         </is>
       </c>
       <c r="J17" s="19" t="inlineStr">
         <is>
-          <t>Mumbai WagonR with 0 trips is billed baseline rate: 7 × ₹970 = ₹6,790.</t>
+          <t>Mumbai WagonR with 0 trips is billed baseline rate: 7 × (970 + 30) = ₹7,000.</t>
         </is>
       </c>
     </row>
@@ -21791,7 +21754,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Flat ₹1,050/day (Indemnity ₹0)</t>
+          <t>Flat ₹1,050/day + ₹30 fee = ₹1,080/day</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -21891,7 +21854,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>WagonR: ₹970, Dzire: ₹1,100, Tigor EV: ₹1,300</t>
+          <t>WagonR: ₹970, Dzire: ₹1,100, Tigor EV: ₹1,300 (+ ₹30 fee)</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -21941,7 +21904,7 @@
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
-          <t>WagonR 6 Tiers: ₹970 to ₹339/day (Indemnity ₹0)</t>
+          <t>WagonR 6 Tiers: ₹970 to ₹339/day + ₹30 fee</t>
         </is>
       </c>
       <c r="H23" s="9" t="inlineStr">

--- a/Rental Final Table/LetzRyd_Rental_Master_Architecture_Complete.xlsx
+++ b/Rental Final Table/LetzRyd_Rental_Master_Architecture_Complete.xlsx
@@ -19940,11 +19940,10 @@
       </c>
       <c r="H5" s="19" t="inlineStr">
         <is>
-          <t>• 0 - 54 trips: ₹929/day
-• 55 - 64 trips: ₹899/day
-• 65 - 74 trips: ₹879/day
-• 75 - 89 trips: ₹869/day
-• 90+ trips: ₹799/day
+          <t>• 0 - 89 trips: ₹929/day
+• 90 - 109 trips: ₹665/day
+• 110 - 129 trips: ₹525/day
+• 130+ trips: ₹400/day
 • Ola trips &gt;= 1: Flat ₹1,050/day</t>
         </is>
       </c>
@@ -19955,8 +19954,8 @@
       </c>
       <c r="J5" s="19" t="inlineStr">
         <is>
-          <t>Driver A completes 68 Uber trips and 0 Ola trips in the week. He lands in the 65-74 tier (₹879/day). For 7 active billable days, Rent = 7 × (879 + 30) = ₹6,363.
-If Driver A did 67 Uber trips and 1 Ola trip, he is penalized: Rent = 7 × (1050 + 30) = ₹7,560.</t>
+          <t>Driver A completes 102 Uber trips and 0 Ola trips in the week. He lands in the 90-109 tier (₹665/day). For 7 active billable days, Rent = 7 × (665 + 30) = ₹4,865.
+If Driver A did 101 Uber trips and 1 Ola trip, he is penalized: Rent = 7 × (1,050 + 30) = ₹7,560.</t>
         </is>
       </c>
     </row>
@@ -20776,7 +20775,7 @@
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>Uber Completed Trips = 68, Ola Completed Trips = 0, Total Trips = 68</t>
+          <t>Uber Completed Trips = 102, Ola Completed Trips = 0, Total Trips = 102</t>
         </is>
       </c>
       <c r="F6" s="24" t="inlineStr">
@@ -20786,7 +20785,7 @@
       </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t>Weekly Trips = 68 (Ola = 0)</t>
+          <t>Weekly Trips = 102 (Ola = 0)</t>
         </is>
       </c>
     </row>
@@ -20882,22 +20881,22 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>city = 'Bangalore', customer_type = 'Individual', vehicle_model = 'WagonR', trips = 68, plan_id = 'BLR_MASTER_IND'</t>
+          <t>city = 'Bangalore', customer_type = 'Individual', vehicle_model = 'WagonR', trips = 102, plan_id = 'BLR_MASTER_IND'</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
         <is>
-          <t>Trip Tier: 65 to 74 trips -&gt; base_daily_rent = ₹879.00/day</t>
+          <t>Trip Tier: 90 to 109 trips -&gt; base_daily_rent = ₹665.00/day</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t>Under BLR_MASTER_IND, because Ola trips = 0, no multi-app penalty is triggered. Driver earns Tier 3 discount (₹879 vs ₹929 base).</t>
+          <t>Under BLR_MASTER_IND, because Ola trips = 0, no multi-app penalty is triggered. Driver earns Tier 2 discount (₹665 vs ₹929 base).</t>
         </is>
       </c>
       <c r="G9" s="19" t="inlineStr">
         <is>
-          <t>Base Daily Rent = ₹879.00/day</t>
+          <t>Base Daily Rent = ₹665.00/day</t>
         </is>
       </c>
     </row>
@@ -20961,17 +20960,17 @@
       </c>
       <c r="E11" s="21" t="inlineStr">
         <is>
-          <t>Row inserted: applied_rent = 879.00, indemnity = 30.00, net_rent = 909.00</t>
+          <t>Row inserted: applied_rent = 665.00, indemnity = 30.00, net_rent = 695.00</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t>Committed into daily rent log with audit rule: 'Priority 3: Dynamic Slab (BLR_MASTER_IND: 65-74)'. Tri-grain protects against handover collisions.</t>
+          <t>Committed into daily rent log with audit rule: 'Priority 3: Dynamic Slab (BLR_MASTER_IND: 90-109)'. Tri-grain protects against handover collisions.</t>
         </is>
       </c>
       <c r="G11" s="19" t="inlineStr">
         <is>
-          <t>Net Daily Rent = ₹909.00/day</t>
+          <t>Net Daily Rent = ₹695.00/day</t>
         </is>
       </c>
     </row>
@@ -20998,7 +20997,7 @@
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>Daily ledger row updated with lease_rental = ₹879.00, indemnity = ₹30.00</t>
+          <t>Daily ledger row updated with lease_rental = ₹665.00, indemnity = ₹30.00</t>
         </is>
       </c>
       <c r="F12" s="24" t="inlineStr">
@@ -21035,7 +21034,7 @@
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>Weekly Lease Rental = 7 × ₹879 = ₹6,153.00 | Weekly Indemnity = 7 × ₹30 = ₹210.00</t>
+          <t>Weekly Lease Rental = 7 × ₹665 = ₹4,655.00 | Weekly Indemnity = 7 × ₹30 = ₹210.00</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -21045,7 +21044,7 @@
       </c>
       <c r="G13" s="19" t="inlineStr">
         <is>
-          <t>TOTAL WEEKLY RENT = ₹6,363.00</t>
+          <t>TOTAL WEEKLY RENT = ₹4,865.00</t>
         </is>
       </c>
     </row>

--- a/Rental Final Table/LetzRyd_Rental_Master_Architecture_Complete.xlsx
+++ b/Rental Final Table/LetzRyd_Rental_Master_Architecture_Complete.xlsx
@@ -1879,7 +1879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2812,7 +2812,7 @@
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B16" s="7" t="n">
         <v>6</v>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>EC3</t>
+          <t>WAGONR</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
@@ -2859,7 +2859,7 @@
         <v>49</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1400</v>
+        <v>989</v>
       </c>
       <c r="M16" s="9" t="n">
         <v>30</v>
@@ -2872,7 +2872,7 @@
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B17" s="11" t="n">
         <v>6</v>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>DZIRE</t>
+          <t>EC3</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -2919,7 +2919,7 @@
         <v>49</v>
       </c>
       <c r="L17" s="13" t="n">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="M17" s="13" t="n">
         <v>30</v>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B18" s="7" t="n">
         <v>6</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>WAGONR</t>
+          <t>DZIRE</t>
         </is>
       </c>
       <c r="H18" s="8" t="inlineStr">
@@ -2979,7 +2979,7 @@
         <v>49</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>989</v>
+        <v>1100</v>
       </c>
       <c r="M18" s="9" t="n">
         <v>30</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B19" s="11" t="n">
         <v>6</v>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>DZIRE</t>
+          <t>EC3</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -3039,7 +3039,7 @@
         <v>59</v>
       </c>
       <c r="L19" s="13" t="n">
-        <v>1009</v>
+        <v>1300</v>
       </c>
       <c r="M19" s="13" t="n">
         <v>30</v>
@@ -3112,7 +3112,7 @@
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B21" s="11" t="n">
         <v>6</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>EC3</t>
+          <t>DZIRE</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -3159,7 +3159,7 @@
         <v>59</v>
       </c>
       <c r="L21" s="13" t="n">
-        <v>1300</v>
+        <v>1009</v>
       </c>
       <c r="M21" s="13" t="n">
         <v>30</v>
@@ -3352,7 +3352,7 @@
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B25" s="11" t="n">
         <v>6</v>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>EC3</t>
+          <t>WAGONR</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -3399,7 +3399,7 @@
         <v>9999</v>
       </c>
       <c r="L25" s="13" t="n">
-        <v>1210</v>
+        <v>799</v>
       </c>
       <c r="M25" s="13" t="n">
         <v>30</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B26" s="7" t="n">
         <v>6</v>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>WAGONR</t>
+          <t>DZIRE</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
@@ -3459,7 +3459,7 @@
         <v>9999</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>799</v>
+        <v>899</v>
       </c>
       <c r="M26" s="9" t="n">
         <v>30</v>
@@ -3472,7 +3472,7 @@
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B27" s="11" t="n">
         <v>6</v>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>DZIRE</t>
+          <t>EC3</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -3519,7 +3519,7 @@
         <v>9999</v>
       </c>
       <c r="L27" s="13" t="n">
-        <v>899</v>
+        <v>1210</v>
       </c>
       <c r="M27" s="13" t="n">
         <v>30</v>
@@ -3532,7 +3532,7 @@
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="7" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B28" s="7" t="n">
         <v>7</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>DZIRE</t>
+          <t>EC3</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
@@ -3579,7 +3579,7 @@
         <v>89</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="M28" s="9" t="n">
         <v>30</v>
@@ -3592,7 +3592,7 @@
     </row>
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="11" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B29" s="11" t="n">
         <v>7</v>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>EC3</t>
+          <t>WAGONR</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -3639,7 +3639,7 @@
         <v>89</v>
       </c>
       <c r="L29" s="13" t="n">
-        <v>1400</v>
+        <v>989</v>
       </c>
       <c r="M29" s="13" t="n">
         <v>30</v>
@@ -3652,7 +3652,7 @@
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B30" s="7" t="n">
         <v>7</v>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>WAGONR</t>
+          <t>DZIRE</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
@@ -3699,7 +3699,7 @@
         <v>89</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>989</v>
+        <v>1100</v>
       </c>
       <c r="M30" s="9" t="n">
         <v>30</v>
@@ -3772,7 +3772,7 @@
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B32" s="7" t="n">
         <v>7</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>WAGONR</t>
+          <t>DZIRE</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
@@ -3819,7 +3819,7 @@
         <v>104</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>679</v>
+        <v>799</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>30</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="11" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B33" s="11" t="n">
         <v>7</v>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>DZIRE</t>
+          <t>WAGONR</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -3879,7 +3879,7 @@
         <v>104</v>
       </c>
       <c r="L33" s="13" t="n">
-        <v>799</v>
+        <v>679</v>
       </c>
       <c r="M33" s="13" t="n">
         <v>30</v>
@@ -3892,7 +3892,7 @@
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B34" s="7" t="n">
         <v>7</v>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>EC3</t>
+          <t>WAGONR</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -3939,7 +3939,7 @@
         <v>119</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>1010</v>
+        <v>599</v>
       </c>
       <c r="M34" s="9" t="n">
         <v>30</v>
@@ -4012,7 +4012,7 @@
     </row>
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B36" s="7" t="n">
         <v>7</v>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>WAGONR</t>
+          <t>EC3</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -4059,7 +4059,7 @@
         <v>119</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>599</v>
+        <v>1010</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>30</v>
@@ -4072,7 +4072,7 @@
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="11" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B37" s="11" t="n">
         <v>7</v>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>WAGONR</t>
+          <t>EC3</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -4119,7 +4119,7 @@
         <v>134</v>
       </c>
       <c r="L37" s="13" t="n">
-        <v>479</v>
+        <v>890</v>
       </c>
       <c r="M37" s="13" t="n">
         <v>30</v>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="7" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B38" s="7" t="n">
         <v>7</v>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>DZIRE</t>
+          <t>WAGONR</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
@@ -4179,7 +4179,7 @@
         <v>134</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>599</v>
+        <v>479</v>
       </c>
       <c r="M38" s="9" t="n">
         <v>30</v>
@@ -4192,7 +4192,7 @@
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="11" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B39" s="11" t="n">
         <v>7</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>EC3</t>
+          <t>DZIRE</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -4239,7 +4239,7 @@
         <v>134</v>
       </c>
       <c r="L39" s="13" t="n">
-        <v>890</v>
+        <v>599</v>
       </c>
       <c r="M39" s="13" t="n">
         <v>30</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="7" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B40" s="7" t="n">
         <v>7</v>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
-          <t>WAGONR</t>
+          <t>EC3</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
@@ -4299,7 +4299,7 @@
         <v>9999</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>379</v>
+        <v>790</v>
       </c>
       <c r="M40" s="9" t="n">
         <v>30</v>
@@ -4372,7 +4372,7 @@
     </row>
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="7" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B42" s="7" t="n">
         <v>7</v>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t>EC3</t>
+          <t>WAGONR</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
@@ -4419,7 +4419,7 @@
         <v>9999</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>790</v>
+        <v>379</v>
       </c>
       <c r="M42" s="9" t="n">
         <v>30</v>
@@ -6292,14 +6292,14 @@
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74" s="7" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B74" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>BLR_OP_RISHAD_EBS</t>
+          <t>BLR_OP_RISHAD_TBS</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -6336,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="K74" s="7" t="n">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="L74" s="9" t="n">
         <v>800</v>
@@ -6346,20 +6346,20 @@
       </c>
       <c r="N74" s="8" t="inlineStr">
         <is>
-          <t>BLR Slabs: Rishad P V EBS &lt;90=800</t>
+          <t>BLR Hisaab Col N IF(AB&lt;55,800)</t>
         </is>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75" s="11" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B75" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>BLR_OP_RISHAD_EBS</t>
+          <t>BLR_OP_RISHAD_TBS</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -6406,20 +6406,20 @@
       </c>
       <c r="N75" s="12" t="inlineStr">
         <is>
-          <t>BLR Slabs: Rishad P V Ola trips flat 1050</t>
+          <t>BLR Hisaab Col N OLA Flat 1050</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="7" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B76" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>BLR_OP_RISHAD_EBS</t>
+          <t>BLR_OP_RISHAD_TBS</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -6453,33 +6453,33 @@
         </is>
       </c>
       <c r="J76" s="7" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>550</v>
+        <v>760</v>
       </c>
       <c r="M76" s="9" t="n">
         <v>20</v>
       </c>
       <c r="N76" s="8" t="inlineStr">
         <is>
-          <t>BLR Slabs: Rishad P V EBS 90+=550</t>
+          <t>BLR Hisaab Col N IF(AB&gt;=55,760)</t>
         </is>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77" s="11" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B77" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>BLR_OP_RISHAD_EBS</t>
+          <t>BLR_OP_RISHAD_TBS</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -6513,33 +6513,33 @@
         </is>
       </c>
       <c r="J77" s="11" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="L77" s="13" t="n">
-        <v>410</v>
+        <v>740</v>
       </c>
       <c r="M77" s="13" t="n">
         <v>20</v>
       </c>
       <c r="N77" s="12" t="inlineStr">
         <is>
-          <t>BLR Slabs: Rishad P V EBS 110+=410</t>
+          <t>BLR Hisaab Col N IF(AB&gt;=65,740)</t>
         </is>
       </c>
     </row>
     <row r="78" ht="20" customHeight="1">
       <c r="A78" s="7" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B78" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>BLR_OP_RISHAD_EBS</t>
+          <t>BLR_OP_RISHAD_TBS</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
@@ -6573,38 +6573,38 @@
         </is>
       </c>
       <c r="J78" s="7" t="n">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="K78" s="7" t="n">
         <v>9999</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>270</v>
+        <v>720</v>
       </c>
       <c r="M78" s="9" t="n">
         <v>20</v>
       </c>
       <c r="N78" s="8" t="inlineStr">
         <is>
-          <t>BLR Slabs: Rishad P V EBS 130+=270</t>
+          <t>BLR Hisaab Col N IF(AB&gt;=75,720)</t>
         </is>
       </c>
     </row>
     <row r="79" ht="20" customHeight="1">
       <c r="A79" s="11" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B79" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>BLR_OP_RAMEES</t>
+          <t>BLR_OP_RISHAD_EBS</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>LETZBLRIP8075280208</t>
+          <t>LETZBLRIP9656907001</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
@@ -6639,32 +6639,32 @@
         <v>89</v>
       </c>
       <c r="L79" s="13" t="n">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N79" s="12" t="inlineStr">
         <is>
-          <t>BLR Slabs: Ramees EBS &lt;90=900</t>
+          <t>BLR Slabs: Rishad P V EBS &lt;90=800</t>
         </is>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80" s="7" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B80" s="7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>BLR_OP_RAMEES</t>
+          <t>BLR_OP_RISHAD_EBS</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>LETZBLRIP8075280208</t>
+          <t>LETZBLRIP9656907001</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
@@ -6684,47 +6684,47 @@
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>UBER_TRIPS</t>
+          <t>OLA_TRIPS</t>
         </is>
       </c>
       <c r="I80" s="8" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>OLA_GE_1</t>
         </is>
       </c>
       <c r="J80" s="7" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>109</v>
+        <v>9999</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>615</v>
+        <v>1050</v>
       </c>
       <c r="M80" s="9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
-          <t>BLR Slabs: Ramees EBS 90+=615</t>
+          <t>BLR Slabs: Rishad P V Ola trips flat 1050</t>
         </is>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81" s="11" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="B81" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>BLR_OP_RAMEES</t>
+          <t>BLR_OP_RISHAD_EBS</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>LETZBLRIP8075280208</t>
+          <t>LETZBLRIP9656907001</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
@@ -6753,78 +6753,378 @@
         </is>
       </c>
       <c r="J81" s="11" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="L81" s="13" t="n">
-        <v>465</v>
+        <v>550</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N81" s="12" t="inlineStr">
         <is>
-          <t>BLR Slabs: Ramees EBS 110+=465</t>
+          <t>BLR Slabs: Rishad P V EBS 90+=550</t>
         </is>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>BLR_OP_RISHAD_EBS</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>LETZBLRIP9656907001</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="G82" s="8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>UBER_TRIPS</t>
+        </is>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J82" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="K82" s="7" t="n">
+        <v>129</v>
+      </c>
+      <c r="L82" s="9" t="n">
+        <v>410</v>
+      </c>
+      <c r="M82" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="N82" s="8" t="inlineStr">
+        <is>
+          <t>BLR Slabs: Rishad P V EBS 110+=410</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="11" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>BLR_OP_RISHAD_EBS</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>LETZBLRIP9656907001</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="F83" s="12" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
+        <is>
+          <t>UBER_TRIPS</t>
+        </is>
+      </c>
+      <c r="I83" s="12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="n">
+        <v>130</v>
+      </c>
+      <c r="K83" s="11" t="n">
+        <v>9999</v>
+      </c>
+      <c r="L83" s="13" t="n">
+        <v>270</v>
+      </c>
+      <c r="M83" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="N83" s="12" t="inlineStr">
+        <is>
+          <t>BLR Slabs: Rishad P V EBS 130+=270</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>BLR_OP_RAMEES</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>LETZBLRIP8075280208</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="G84" s="8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>UBER_TRIPS</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="7" t="n">
+        <v>89</v>
+      </c>
+      <c r="L84" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="M84" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="N84" s="8" t="inlineStr">
+        <is>
+          <t>BLR Slabs: Ramees EBS &lt;90=900</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="B85" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>BLR_OP_RAMEES</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>LETZBLRIP8075280208</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="F85" s="12" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="inlineStr">
+        <is>
+          <t>UBER_TRIPS</t>
+        </is>
+      </c>
+      <c r="I85" s="12" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="n">
+        <v>90</v>
+      </c>
+      <c r="K85" s="11" t="n">
+        <v>109</v>
+      </c>
+      <c r="L85" s="13" t="n">
+        <v>615</v>
+      </c>
+      <c r="M85" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="N85" s="12" t="inlineStr">
+        <is>
+          <t>BLR Slabs: Ramees EBS 90+=615</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>BLR_OP_RAMEES</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr">
+        <is>
+          <t>LETZBLRIP8075280208</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>Operator</t>
+        </is>
+      </c>
+      <c r="G86" s="8" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>UBER_TRIPS</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="J86" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="K86" s="7" t="n">
+        <v>129</v>
+      </c>
+      <c r="L86" s="9" t="n">
+        <v>465</v>
+      </c>
+      <c r="M86" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="N86" s="8" t="inlineStr">
+        <is>
+          <t>BLR Slabs: Ramees EBS 110+=465</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="B82" s="7" t="n">
+      <c r="B87" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C87" s="12" t="inlineStr">
         <is>
           <t>BLR_OP_RAMEES</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D87" s="12" t="inlineStr">
         <is>
           <t>LETZBLRIP8075280208</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="E87" s="12" t="inlineStr">
         <is>
           <t>Bangalore</t>
         </is>
       </c>
-      <c r="F82" s="8" t="inlineStr">
+      <c r="F87" s="12" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
-      <c r="G82" s="8" t="inlineStr">
+      <c r="G87" s="12" t="inlineStr">
         <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="H82" s="8" t="inlineStr">
+      <c r="H87" s="12" t="inlineStr">
         <is>
           <t>UBER_TRIPS</t>
         </is>
       </c>
-      <c r="I82" s="8" t="inlineStr">
+      <c r="I87" s="12" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="J82" s="7" t="n">
+      <c r="J87" s="11" t="n">
         <v>130</v>
       </c>
-      <c r="K82" s="7" t="n">
+      <c r="K87" s="11" t="n">
         <v>9999</v>
       </c>
-      <c r="L82" s="9" t="n">
+      <c r="L87" s="13" t="n">
         <v>320</v>
       </c>
-      <c r="M82" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="N82" s="8" t="inlineStr">
+      <c r="M87" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="N87" s="12" t="inlineStr">
         <is>
           <t>BLR Slabs: Ramees EBS 130+=320</t>
         </is>
@@ -20699,7 +20999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -20708,7 +21008,7 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="65" customWidth="1" min="7" max="7"/>
+    <col width="63" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
@@ -20799,11 +21099,11 @@
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -20813,7 +21113,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>Hyundai Xcent</t>
         </is>
       </c>
       <c r="E3" s="13" t="n">
@@ -20824,7 +21124,7 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Mumbai city indemnity fee waiver policy (all vehicles ₹0 fee)</t>
+          <t>Hyundai Xcent retired fleet indemnity waiver</t>
         </is>
       </c>
       <c r="H3" s="16" t="n">
@@ -20836,7 +21136,7 @@
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
@@ -20845,14 +21145,14 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
+          <t>LETZHYDIP9701685282</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
           <t>ALL</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Hyundai Xcent</t>
-        </is>
-      </c>
       <c r="E4" s="9" t="n">
         <v>0</v>
       </c>
@@ -20861,7 +21161,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Hyundai Xcent retired fleet indemnity waiver</t>
+          <t>Shaik Kareem indemnity waiver</t>
         </is>
       </c>
       <c r="H4" s="15" t="n">
@@ -20873,7 +21173,7 @@
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
@@ -20882,7 +21182,7 @@
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>LETZHYDIP9701685282</t>
+          <t>LETZHYDIP9885838038</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -20910,16 +21210,16 @@
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>LETZHYDIP9885838038</t>
+          <t>LETZBLRIP9036461336</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -20928,14 +21228,14 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F6" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Shaik Kareem indemnity waiver</t>
+          <t>Nisamudeen K P negotiated indemnity rate ₹15/day</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
@@ -20947,7 +21247,7 @@
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
@@ -20956,7 +21256,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>LETZBLRIP9036461336</t>
+          <t>LETZBLRIP9656907001</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -20965,14 +21265,14 @@
         </is>
       </c>
       <c r="E7" s="13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F7" s="14" t="b">
         <v>0</v>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Nisamudeen K P negotiated indemnity rate ₹15/day</t>
+          <t>Rishad P V negotiated indemnity rate ₹20/day</t>
         </is>
       </c>
       <c r="H7" s="16" t="n">
@@ -20984,75 +21284,38 @@
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>LETZBLRIP9656907001</t>
+          <t>ALL</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>Xcent</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F8" s="10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Rishad P V negotiated indemnity rate ₹20/day</t>
+          <t>Hyundai Xcent / Prime T BSIV retired fleet indemnity waiver</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
         <v>46023</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>2958465</v>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Xcent</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>Hyundai Xcent / Prime T BSIV retired fleet indemnity waiver</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>46023</v>
-      </c>
-      <c r="I9" s="16" t="n">
         <v>2958465</v>
       </c>
     </row>
@@ -21194,7 +21457,7 @@
     <col width="19" customWidth="1" min="14" max="14"/>
     <col width="19" customWidth="1" min="15" max="15"/>
     <col width="26" customWidth="1" min="16" max="16"/>
-    <col width="101" customWidth="1" min="17" max="17"/>
+    <col width="95" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -21337,7 +21600,7 @@
         <v>1080</v>
       </c>
       <c r="N2" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O2" s="7" t="n"/>
       <c r="P2" s="7" t="n">
@@ -21402,7 +21665,7 @@
         <v>980</v>
       </c>
       <c r="N3" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O3" s="11" t="n"/>
       <c r="P3" s="11" t="n">
@@ -21466,16 +21729,12 @@
       <c r="M4" s="9" t="n">
         <v>959</v>
       </c>
-      <c r="N4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="7" t="n">
-        <v>35</v>
-      </c>
+      <c r="N4" s="7" t="n"/>
+      <c r="O4" s="7" t="n"/>
       <c r="P4" s="7" t="n"/>
       <c r="Q4" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -21532,15 +21791,15 @@
         <v>959</v>
       </c>
       <c r="N5" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O5" s="11" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P5" s="11" t="n"/>
       <c r="Q5" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -21666,7 +21925,7 @@
       <c r="P7" s="11" t="n"/>
       <c r="Q7" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55, Partner: LETZBLRIP7026684292)</t>
+          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55)</t>
         </is>
       </c>
     </row>
@@ -21714,24 +21973,20 @@
         <v>0</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>900</v>
+        <v>929</v>
       </c>
       <c r="L8" s="9" t="n">
         <v>30</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>930</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" s="7" t="n">
-        <v>40</v>
-      </c>
+        <v>959</v>
+      </c>
+      <c r="N8" s="7" t="n"/>
+      <c r="O8" s="7" t="n"/>
       <c r="P8" s="7" t="n"/>
       <c r="Q8" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -21796,7 +22051,7 @@
       <c r="P9" s="11" t="n"/>
       <c r="Q9" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #77, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #77)</t>
         </is>
       </c>
     </row>
@@ -21844,24 +22099,24 @@
         <v>56</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>899</v>
+        <v>929</v>
       </c>
       <c r="L10" s="9" t="n">
         <v>30</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>929</v>
+        <v>959</v>
       </c>
       <c r="N10" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O10" s="7" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="P10" s="7" t="n"/>
       <c r="Q10" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #45, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35)</t>
         </is>
       </c>
     </row>
@@ -21987,7 +22242,7 @@
       <c r="P12" s="7" t="n"/>
       <c r="Q12" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #59, Partner: LETZBLRIP7356813050)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #59)</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22589,7 @@
         </is>
       </c>
       <c r="I18" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="7" t="n">
         <v>3</v>
@@ -22353,7 +22608,7 @@
       <c r="P18" s="7" t="n"/>
       <c r="Q18" s="8" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -22395,7 +22650,7 @@
         </is>
       </c>
       <c r="I19" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" s="11" t="n">
         <v>4</v>
@@ -22414,7 +22669,7 @@
       <c r="P19" s="11" t="n"/>
       <c r="Q19" s="12" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -22967,7 +23222,7 @@
       <c r="P28" s="7" t="n"/>
       <c r="Q28" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #36, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #36)</t>
         </is>
       </c>
     </row>
@@ -23032,7 +23287,7 @@
       <c r="P29" s="11" t="n"/>
       <c r="Q29" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35)</t>
         </is>
       </c>
     </row>
@@ -23088,16 +23343,12 @@
       <c r="M30" s="9" t="n">
         <v>959</v>
       </c>
-      <c r="N30" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="7" t="n">
-        <v>35</v>
-      </c>
+      <c r="N30" s="7" t="n"/>
+      <c r="O30" s="7" t="n"/>
       <c r="P30" s="7" t="n"/>
       <c r="Q30" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -23162,7 +23413,7 @@
       <c r="P31" s="11" t="n"/>
       <c r="Q31" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -23227,7 +23478,7 @@
       <c r="P32" s="7" t="n"/>
       <c r="Q32" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -23292,7 +23543,7 @@
       <c r="P33" s="11" t="n"/>
       <c r="Q33" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #41, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #41)</t>
         </is>
       </c>
     </row>
@@ -23418,7 +23669,7 @@
       <c r="P35" s="11" t="n"/>
       <c r="Q35" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -23475,15 +23726,15 @@
         <v>1430</v>
       </c>
       <c r="N36" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O36" s="7" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="P36" s="7" t="n"/>
       <c r="Q36" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #9, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #23)</t>
         </is>
       </c>
     </row>
@@ -23670,7 +23921,7 @@
       <c r="P39" s="11" t="n"/>
       <c r="Q39" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55, Partner: LETZBLRIP7026684292)</t>
+          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55)</t>
         </is>
       </c>
     </row>
@@ -23857,7 +24108,7 @@
       <c r="P42" s="7" t="n"/>
       <c r="Q42" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -23922,7 +24173,7 @@
       <c r="P43" s="11" t="n"/>
       <c r="Q43" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -23978,16 +24229,12 @@
       <c r="M44" s="9" t="n">
         <v>959</v>
       </c>
-      <c r="N44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O44" s="7" t="n">
-        <v>35</v>
-      </c>
+      <c r="N44" s="7" t="n"/>
+      <c r="O44" s="7" t="n"/>
       <c r="P44" s="7" t="n"/>
       <c r="Q44" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -24035,24 +24282,24 @@
         <v>70</v>
       </c>
       <c r="K45" s="13" t="n">
-        <v>800</v>
+        <v>740</v>
       </c>
       <c r="L45" s="13" t="n">
         <v>20</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>820</v>
+        <v>760</v>
       </c>
       <c r="N45" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O45" s="11" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="P45" s="11" t="n"/>
       <c r="Q45" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #84)</t>
         </is>
       </c>
     </row>
@@ -24170,7 +24417,7 @@
         <v>1080</v>
       </c>
       <c r="N47" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O47" s="11" t="n"/>
       <c r="P47" s="11" t="n">
@@ -24356,16 +24603,12 @@
       <c r="M50" s="9" t="n">
         <v>959</v>
       </c>
-      <c r="N50" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O50" s="7" t="n">
-        <v>35</v>
-      </c>
+      <c r="N50" s="7" t="n"/>
+      <c r="O50" s="7" t="n"/>
       <c r="P50" s="7" t="n"/>
       <c r="Q50" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -24474,24 +24717,24 @@
         <v>75</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>800</v>
+        <v>720</v>
       </c>
       <c r="L52" s="9" t="n">
         <v>20</v>
       </c>
       <c r="M52" s="9" t="n">
-        <v>820</v>
+        <v>740</v>
       </c>
       <c r="N52" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O52" s="7" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="P52" s="7" t="n"/>
       <c r="Q52" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #85)</t>
         </is>
       </c>
     </row>
@@ -24556,7 +24799,7 @@
       <c r="P53" s="11" t="n"/>
       <c r="Q53" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -24613,15 +24856,15 @@
         <v>1019</v>
       </c>
       <c r="N54" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O54" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P54" s="7" t="n"/>
       <c r="Q54" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #1, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #13)</t>
         </is>
       </c>
     </row>
@@ -24678,7 +24921,7 @@
         <v>980</v>
       </c>
       <c r="N55" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O55" s="11" t="n"/>
       <c r="P55" s="11" t="n">
@@ -24743,7 +24986,7 @@
         <v>1080</v>
       </c>
       <c r="N56" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O56" s="7" t="n"/>
       <c r="P56" s="7" t="n">
@@ -24930,7 +25173,7 @@
         <v>930</v>
       </c>
       <c r="N59" s="11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O59" s="11" t="n"/>
       <c r="P59" s="11" t="n">
@@ -25003,7 +25246,7 @@
       <c r="P60" s="7" t="n"/>
       <c r="Q60" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #14, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #14)</t>
         </is>
       </c>
     </row>
@@ -25051,24 +25294,24 @@
         <v>79</v>
       </c>
       <c r="K61" s="13" t="n">
-        <v>799</v>
+        <v>989</v>
       </c>
       <c r="L61" s="13" t="n">
         <v>30</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>829</v>
+        <v>1019</v>
       </c>
       <c r="N61" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O61" s="11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P61" s="11" t="n"/>
       <c r="Q61" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #4, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #13)</t>
         </is>
       </c>
     </row>
@@ -25125,7 +25368,7 @@
         <v>980</v>
       </c>
       <c r="N62" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O62" s="7" t="n"/>
       <c r="P62" s="7" t="n">
@@ -25190,7 +25433,7 @@
         <v>970</v>
       </c>
       <c r="N63" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O63" s="11" t="n"/>
       <c r="P63" s="11" t="n">
@@ -25254,16 +25497,12 @@
       <c r="M64" s="9" t="n">
         <v>959</v>
       </c>
-      <c r="N64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O64" s="7" t="n">
-        <v>35</v>
-      </c>
+      <c r="N64" s="7" t="n"/>
+      <c r="O64" s="7" t="n"/>
       <c r="P64" s="7" t="n"/>
       <c r="Q64" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -25328,7 +25567,7 @@
       <c r="P65" s="11" t="n"/>
       <c r="Q65" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #41, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #41)</t>
         </is>
       </c>
     </row>
@@ -25385,7 +25624,7 @@
         <v>1080</v>
       </c>
       <c r="N66" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O66" s="7" t="n"/>
       <c r="P66" s="7" t="n">
@@ -25458,7 +25697,7 @@
       <c r="P67" s="11" t="n"/>
       <c r="Q67" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -25506,24 +25745,24 @@
         <v>72</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>799</v>
+        <v>989</v>
       </c>
       <c r="L68" s="9" t="n">
         <v>30</v>
       </c>
       <c r="M68" s="9" t="n">
-        <v>829</v>
+        <v>1019</v>
       </c>
       <c r="N68" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O68" s="7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P68" s="7" t="n"/>
       <c r="Q68" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #4, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #13)</t>
         </is>
       </c>
     </row>
@@ -25580,7 +25819,7 @@
         <v>1080</v>
       </c>
       <c r="N69" s="11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O69" s="11" t="n"/>
       <c r="P69" s="11" t="n">
@@ -25645,7 +25884,7 @@
         <v>930</v>
       </c>
       <c r="N70" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O70" s="7" t="n"/>
       <c r="P70" s="7" t="n">
@@ -25710,15 +25949,15 @@
         <v>959</v>
       </c>
       <c r="N71" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O71" s="11" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P71" s="11" t="n"/>
       <c r="Q71" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -25775,7 +26014,7 @@
         <v>970</v>
       </c>
       <c r="N72" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O72" s="7" t="n"/>
       <c r="P72" s="7" t="n">
@@ -25840,7 +26079,7 @@
         <v>1080</v>
       </c>
       <c r="N73" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O73" s="11" t="n"/>
       <c r="P73" s="11" t="n">
@@ -26035,7 +26274,7 @@
       <c r="P76" s="7" t="n"/>
       <c r="Q76" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -26092,7 +26331,7 @@
         <v>980</v>
       </c>
       <c r="N77" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O77" s="11" t="n"/>
       <c r="P77" s="11" t="n">
@@ -26218,7 +26457,7 @@
         <v>1080</v>
       </c>
       <c r="N79" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O79" s="11" t="n"/>
       <c r="P79" s="11" t="n">
@@ -26274,24 +26513,24 @@
         <v>72</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>799</v>
+        <v>989</v>
       </c>
       <c r="L80" s="9" t="n">
         <v>30</v>
       </c>
       <c r="M80" s="9" t="n">
-        <v>829</v>
+        <v>1019</v>
       </c>
       <c r="N80" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O80" s="7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P80" s="7" t="n"/>
       <c r="Q80" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #4, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #13)</t>
         </is>
       </c>
     </row>
@@ -26356,7 +26595,7 @@
       <c r="P81" s="11" t="n"/>
       <c r="Q81" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -26543,7 +26782,7 @@
       <c r="P84" s="7" t="n"/>
       <c r="Q84" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -26608,7 +26847,7 @@
       <c r="P85" s="11" t="n"/>
       <c r="Q85" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -26665,15 +26904,15 @@
         <v>1019</v>
       </c>
       <c r="N86" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O86" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P86" s="7" t="n"/>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #1, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #13)</t>
         </is>
       </c>
     </row>
@@ -26860,7 +27099,7 @@
       <c r="P89" s="11" t="n"/>
       <c r="Q89" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #1, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #1)</t>
         </is>
       </c>
     </row>
@@ -26908,24 +27147,24 @@
         <v>75</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>799</v>
+        <v>989</v>
       </c>
       <c r="L90" s="9" t="n">
         <v>30</v>
       </c>
       <c r="M90" s="9" t="n">
-        <v>829</v>
+        <v>1019</v>
       </c>
       <c r="N90" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O90" s="7" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P90" s="7" t="n"/>
       <c r="Q90" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #4, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #13)</t>
         </is>
       </c>
     </row>
@@ -26982,7 +27221,7 @@
         <v>1080</v>
       </c>
       <c r="N91" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O91" s="11" t="n"/>
       <c r="P91" s="11" t="n">
@@ -27046,16 +27285,12 @@
       <c r="M92" s="9" t="n">
         <v>959</v>
       </c>
-      <c r="N92" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O92" s="7" t="n">
-        <v>35</v>
-      </c>
+      <c r="N92" s="7" t="n"/>
+      <c r="O92" s="7" t="n"/>
       <c r="P92" s="7" t="n"/>
       <c r="Q92" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -27106,10 +27341,10 @@
         <v>659</v>
       </c>
       <c r="L93" s="13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M93" s="13" t="n">
-        <v>659</v>
+        <v>689</v>
       </c>
       <c r="N93" s="11" t="n">
         <v>10</v>
@@ -27120,7 +27355,7 @@
       <c r="P93" s="11" t="n"/>
       <c r="Q93" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #10: MUM_UBER_REDUCING, Slab #30, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #10: MUM_UBER_REDUCING, Slab #30)</t>
         </is>
       </c>
     </row>
@@ -27177,7 +27412,7 @@
         <v>970</v>
       </c>
       <c r="N94" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O94" s="7" t="n"/>
       <c r="P94" s="7" t="n">
@@ -27303,7 +27538,7 @@
         <v>930</v>
       </c>
       <c r="N96" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O96" s="7" t="n"/>
       <c r="P96" s="7" t="n">
@@ -27429,7 +27664,7 @@
         <v>1080</v>
       </c>
       <c r="N98" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O98" s="7" t="n"/>
       <c r="P98" s="7" t="n">
@@ -27485,24 +27720,24 @@
         <v>61</v>
       </c>
       <c r="K99" s="13" t="n">
-        <v>899</v>
+        <v>929</v>
       </c>
       <c r="L99" s="13" t="n">
         <v>30</v>
       </c>
       <c r="M99" s="13" t="n">
-        <v>929</v>
+        <v>959</v>
       </c>
       <c r="N99" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O99" s="11" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="P99" s="11" t="n"/>
       <c r="Q99" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #45, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35)</t>
         </is>
       </c>
     </row>
@@ -27567,7 +27802,7 @@
       <c r="P100" s="7" t="n"/>
       <c r="Q100" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -27632,7 +27867,7 @@
       <c r="P101" s="11" t="n"/>
       <c r="Q101" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #57, Partner: LETZBLRIP7356813050)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #57)</t>
         </is>
       </c>
     </row>
@@ -27758,7 +27993,7 @@
       <c r="P103" s="11" t="n"/>
       <c r="Q103" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #61, Partner: LETZBLRIP7306249935)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #61)</t>
         </is>
       </c>
     </row>
@@ -27876,7 +28111,7 @@
         <v>1080</v>
       </c>
       <c r="N105" s="11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O105" s="11" t="n"/>
       <c r="P105" s="11" t="n">
@@ -28001,16 +28236,12 @@
       <c r="M107" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N107" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O107" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N107" s="11" t="n"/>
+      <c r="O107" s="11" t="n"/>
       <c r="P107" s="11" t="n"/>
       <c r="Q107" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -28075,7 +28306,7 @@
       <c r="P108" s="7" t="n"/>
       <c r="Q108" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -28140,7 +28371,7 @@
       <c r="P109" s="11" t="n"/>
       <c r="Q109" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56, Partner: LETZBLRIP7356813050)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56)</t>
         </is>
       </c>
     </row>
@@ -28205,7 +28436,7 @@
       <c r="P110" s="7" t="n"/>
       <c r="Q110" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #46, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #46)</t>
         </is>
       </c>
     </row>
@@ -28514,7 +28745,7 @@
       <c r="P115" s="11" t="n"/>
       <c r="Q115" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #52, Partner: LETZBLRIP7026684292)</t>
+          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #52)</t>
         </is>
       </c>
     </row>
@@ -28579,7 +28810,7 @@
       <c r="P116" s="7" t="n"/>
       <c r="Q116" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -28644,7 +28875,7 @@
       <c r="P117" s="11" t="n"/>
       <c r="Q117" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -28686,7 +28917,7 @@
         </is>
       </c>
       <c r="I118" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118" s="7" t="n">
         <v>27</v>
@@ -28705,7 +28936,7 @@
       <c r="P118" s="7" t="n"/>
       <c r="Q118" s="8" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -28808,7 +29039,7 @@
         </is>
       </c>
       <c r="I120" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" s="7" t="n">
         <v>66</v>
@@ -28827,7 +29058,7 @@
       <c r="P120" s="7" t="n"/>
       <c r="Q120" s="8" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -28892,7 +29123,7 @@
       <c r="P121" s="11" t="n"/>
       <c r="Q121" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -28949,7 +29180,7 @@
         <v>970</v>
       </c>
       <c r="N122" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O122" s="7" t="n"/>
       <c r="P122" s="7" t="n">
@@ -29075,15 +29306,15 @@
         <v>959</v>
       </c>
       <c r="N124" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O124" s="7" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P124" s="7" t="n"/>
       <c r="Q124" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -29148,7 +29379,7 @@
       <c r="P125" s="11" t="n"/>
       <c r="Q125" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #69, Partner: LETZBLRIP7025077468)</t>
+          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #69)</t>
         </is>
       </c>
     </row>
@@ -29205,7 +29436,7 @@
         <v>980</v>
       </c>
       <c r="N126" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O126" s="7" t="n"/>
       <c r="P126" s="7" t="n">
@@ -29270,7 +29501,7 @@
         <v>930</v>
       </c>
       <c r="N127" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O127" s="11" t="n"/>
       <c r="P127" s="11" t="n">
@@ -29335,15 +29566,15 @@
         <v>1430</v>
       </c>
       <c r="N128" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O128" s="7" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="P128" s="7" t="n"/>
       <c r="Q128" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #9, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #23)</t>
         </is>
       </c>
     </row>
@@ -29408,7 +29639,7 @@
       <c r="P129" s="11" t="n"/>
       <c r="Q129" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #42, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #42)</t>
         </is>
       </c>
     </row>
@@ -29465,15 +29696,15 @@
         <v>959</v>
       </c>
       <c r="N130" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O130" s="7" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P130" s="7" t="n"/>
       <c r="Q130" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -29538,7 +29769,7 @@
       <c r="P131" s="11" t="n"/>
       <c r="Q131" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -29595,7 +29826,7 @@
         <v>970</v>
       </c>
       <c r="N132" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O132" s="7" t="n"/>
       <c r="P132" s="7" t="n">
@@ -29668,7 +29899,7 @@
       <c r="P133" s="11" t="n"/>
       <c r="Q133" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -29907,16 +30138,12 @@
       <c r="M137" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N137" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O137" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N137" s="11" t="n"/>
+      <c r="O137" s="11" t="n"/>
       <c r="P137" s="11" t="n"/>
       <c r="Q137" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30261,7 @@
         <v>1080</v>
       </c>
       <c r="N139" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O139" s="11" t="n"/>
       <c r="P139" s="11" t="n">
@@ -30099,7 +30326,7 @@
         <v>970</v>
       </c>
       <c r="N140" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O140" s="7" t="n"/>
       <c r="P140" s="7" t="n">
@@ -30164,7 +30391,7 @@
         <v>1100</v>
       </c>
       <c r="N141" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O141" s="11" t="n"/>
       <c r="P141" s="11" t="n">
@@ -30290,7 +30517,7 @@
         <v>1000</v>
       </c>
       <c r="N143" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O143" s="11" t="n"/>
       <c r="P143" s="11" t="n">
@@ -30355,7 +30582,7 @@
         <v>960</v>
       </c>
       <c r="N144" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O144" s="7" t="n"/>
       <c r="P144" s="7" t="n">
@@ -30420,7 +30647,7 @@
         <v>980</v>
       </c>
       <c r="N145" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O145" s="11" t="n"/>
       <c r="P145" s="11" t="n">
@@ -30607,7 +30834,7 @@
         <v>970</v>
       </c>
       <c r="N148" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O148" s="7" t="n"/>
       <c r="P148" s="7" t="n">
@@ -30666,10 +30893,10 @@
         <v>970</v>
       </c>
       <c r="L149" s="13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M149" s="13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="N149" s="11" t="n">
         <v>10</v>
@@ -30680,7 +30907,7 @@
       <c r="P149" s="11" t="n"/>
       <c r="Q149" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #10: MUM_UBER_REDUCING, Slab #28, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #10: MUM_UBER_REDUCING, Slab #28)</t>
         </is>
       </c>
     </row>
@@ -30737,7 +30964,7 @@
         <v>1000</v>
       </c>
       <c r="N150" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O150" s="7" t="n"/>
       <c r="P150" s="7" t="n">
@@ -30871,7 +31098,7 @@
       <c r="P152" s="7" t="n"/>
       <c r="Q152" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -30988,16 +31215,12 @@
       <c r="M154" s="9" t="n">
         <v>959</v>
       </c>
-      <c r="N154" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O154" s="7" t="n">
-        <v>35</v>
-      </c>
+      <c r="N154" s="7" t="n"/>
+      <c r="O154" s="7" t="n"/>
       <c r="P154" s="7" t="n"/>
       <c r="Q154" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -31045,24 +31268,24 @@
         <v>80</v>
       </c>
       <c r="K155" s="13" t="n">
-        <v>799</v>
+        <v>989</v>
       </c>
       <c r="L155" s="13" t="n">
         <v>30</v>
       </c>
       <c r="M155" s="13" t="n">
-        <v>829</v>
+        <v>1019</v>
       </c>
       <c r="N155" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O155" s="11" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P155" s="11" t="n"/>
       <c r="Q155" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #4, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #13)</t>
         </is>
       </c>
     </row>
@@ -31119,7 +31342,7 @@
         <v>980</v>
       </c>
       <c r="N156" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O156" s="7" t="n"/>
       <c r="P156" s="7" t="n">
@@ -31239,10 +31462,10 @@
         <v>1100</v>
       </c>
       <c r="L158" s="9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M158" s="9" t="n">
-        <v>1100</v>
+        <v>1130</v>
       </c>
       <c r="N158" s="7" t="n"/>
       <c r="O158" s="7" t="n"/>
@@ -31306,7 +31529,7 @@
         <v>930</v>
       </c>
       <c r="N159" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O159" s="11" t="n"/>
       <c r="P159" s="11" t="n">
@@ -31440,7 +31663,7 @@
       <c r="P161" s="11" t="n"/>
       <c r="Q161" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -31505,7 +31728,7 @@
       <c r="P162" s="7" t="n"/>
       <c r="Q162" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -31623,7 +31846,7 @@
         <v>1080</v>
       </c>
       <c r="N164" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O164" s="7" t="n"/>
       <c r="P164" s="7" t="n">
@@ -31810,7 +32033,7 @@
         <v>1080</v>
       </c>
       <c r="N167" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O167" s="11" t="n"/>
       <c r="P167" s="11" t="n">
@@ -31875,7 +32098,7 @@
         <v>1080</v>
       </c>
       <c r="N168" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O168" s="7" t="n"/>
       <c r="P168" s="7" t="n">
@@ -31992,24 +32215,24 @@
         <v>106</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>665</v>
+        <v>869</v>
       </c>
       <c r="L170" s="9" t="n">
         <v>30</v>
       </c>
       <c r="M170" s="9" t="n">
-        <v>695</v>
+        <v>899</v>
       </c>
       <c r="N170" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O170" s="7" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="P170" s="7" t="n"/>
       <c r="Q170" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #36, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #47)</t>
         </is>
       </c>
     </row>
@@ -32135,7 +32358,7 @@
       <c r="P172" s="7" t="n"/>
       <c r="Q172" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55, Partner: LETZBLRIP7026684292)</t>
+          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55)</t>
         </is>
       </c>
     </row>
@@ -32383,7 +32606,7 @@
       <c r="P176" s="7" t="n"/>
       <c r="Q176" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #71, Partner: LETZBLRIP7025077468)</t>
+          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #71)</t>
         </is>
       </c>
     </row>
@@ -32439,16 +32662,12 @@
       <c r="M177" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N177" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O177" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N177" s="11" t="n"/>
+      <c r="O177" s="11" t="n"/>
       <c r="P177" s="11" t="n"/>
       <c r="Q177" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -32513,7 +32732,7 @@
       <c r="P178" s="7" t="n"/>
       <c r="Q178" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #1, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #1)</t>
         </is>
       </c>
     </row>
@@ -32570,7 +32789,7 @@
         <v>970</v>
       </c>
       <c r="N179" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O179" s="11" t="n"/>
       <c r="P179" s="11" t="n">
@@ -32635,7 +32854,7 @@
         <v>970</v>
       </c>
       <c r="N180" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O180" s="7" t="n"/>
       <c r="P180" s="7" t="n">
@@ -32700,15 +32919,15 @@
         <v>959</v>
       </c>
       <c r="N181" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O181" s="11" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P181" s="11" t="n"/>
       <c r="Q181" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -32933,7 +33152,7 @@
         </is>
       </c>
       <c r="I185" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J185" s="11" t="n">
         <v>18</v>
@@ -32952,7 +33171,7 @@
       <c r="P185" s="11" t="n"/>
       <c r="Q185" s="12" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -33070,7 +33289,7 @@
         <v>1080</v>
       </c>
       <c r="N187" s="11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O187" s="11" t="n"/>
       <c r="P187" s="11" t="n">
@@ -33196,7 +33415,7 @@
         <v>1080</v>
       </c>
       <c r="N189" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O189" s="11" t="n"/>
       <c r="P189" s="11" t="n">
@@ -33269,7 +33488,7 @@
       <c r="P190" s="7" t="n"/>
       <c r="Q190" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -33334,7 +33553,7 @@
       <c r="P191" s="11" t="n"/>
       <c r="Q191" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #45, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #45)</t>
         </is>
       </c>
     </row>
@@ -33376,7 +33595,7 @@
         </is>
       </c>
       <c r="I192" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J192" s="7" t="n">
         <v>2</v>
@@ -33395,7 +33614,7 @@
       <c r="P192" s="7" t="n"/>
       <c r="Q192" s="8" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -33452,7 +33671,7 @@
         <v>1100</v>
       </c>
       <c r="N193" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O193" s="11" t="n"/>
       <c r="P193" s="11" t="n">
@@ -33517,15 +33736,15 @@
         <v>959</v>
       </c>
       <c r="N194" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O194" s="7" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P194" s="7" t="n"/>
       <c r="Q194" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -33573,24 +33792,24 @@
         <v>64</v>
       </c>
       <c r="K195" s="13" t="n">
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="L195" s="13" t="n">
         <v>20</v>
       </c>
       <c r="M195" s="13" t="n">
-        <v>820</v>
+        <v>780</v>
       </c>
       <c r="N195" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O195" s="11" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="P195" s="11" t="n"/>
       <c r="Q195" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #83)</t>
         </is>
       </c>
     </row>
@@ -33769,15 +33988,15 @@
         <v>959</v>
       </c>
       <c r="N198" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O198" s="7" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P198" s="7" t="n"/>
       <c r="Q198" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -33955,16 +34174,12 @@
       <c r="M201" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N201" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O201" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N201" s="11" t="n"/>
+      <c r="O201" s="11" t="n"/>
       <c r="P201" s="11" t="n"/>
       <c r="Q201" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -34090,7 +34305,7 @@
       <c r="P203" s="11" t="n"/>
       <c r="Q203" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #65, Partner: LETZBLRIP8075280208)</t>
+          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #65)</t>
         </is>
       </c>
     </row>
@@ -34254,7 +34469,7 @@
         </is>
       </c>
       <c r="I206" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J206" s="7" t="n">
         <v>13</v>
@@ -34273,7 +34488,7 @@
       <c r="P206" s="7" t="n"/>
       <c r="Q206" s="8" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -34329,16 +34544,12 @@
       <c r="M207" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N207" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O207" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N207" s="11" t="n"/>
+      <c r="O207" s="11" t="n"/>
       <c r="P207" s="11" t="n"/>
       <c r="Q207" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -34395,7 +34606,7 @@
         <v>1080</v>
       </c>
       <c r="N208" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O208" s="7" t="n"/>
       <c r="P208" s="7" t="n">
@@ -34451,24 +34662,24 @@
         <v>65</v>
       </c>
       <c r="K209" s="13" t="n">
-        <v>800</v>
+        <v>740</v>
       </c>
       <c r="L209" s="13" t="n">
         <v>20</v>
       </c>
       <c r="M209" s="13" t="n">
-        <v>820</v>
+        <v>760</v>
       </c>
       <c r="N209" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O209" s="11" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="P209" s="11" t="n"/>
       <c r="Q209" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #84)</t>
         </is>
       </c>
     </row>
@@ -34533,7 +34744,7 @@
       <c r="P210" s="7" t="n"/>
       <c r="Q210" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #9, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #9)</t>
         </is>
       </c>
     </row>
@@ -34659,7 +34870,7 @@
       <c r="P212" s="7" t="n"/>
       <c r="Q212" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -34785,7 +34996,7 @@
       <c r="P214" s="7" t="n"/>
       <c r="Q214" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56, Partner: LETZBLRIP7356813050)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56)</t>
         </is>
       </c>
     </row>
@@ -34833,24 +35044,24 @@
         <v>56</v>
       </c>
       <c r="K215" s="13" t="n">
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="L215" s="13" t="n">
         <v>20</v>
       </c>
       <c r="M215" s="13" t="n">
-        <v>820</v>
+        <v>780</v>
       </c>
       <c r="N215" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O215" s="11" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="P215" s="11" t="n"/>
       <c r="Q215" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #83)</t>
         </is>
       </c>
     </row>
@@ -34898,24 +35109,24 @@
         <v>73</v>
       </c>
       <c r="K216" s="9" t="n">
-        <v>800</v>
+        <v>740</v>
       </c>
       <c r="L216" s="9" t="n">
         <v>20</v>
       </c>
       <c r="M216" s="9" t="n">
-        <v>820</v>
+        <v>760</v>
       </c>
       <c r="N216" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O216" s="7" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="P216" s="7" t="n"/>
       <c r="Q216" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #84)</t>
         </is>
       </c>
     </row>
@@ -34963,24 +35174,24 @@
         <v>76</v>
       </c>
       <c r="K217" s="13" t="n">
-        <v>800</v>
+        <v>720</v>
       </c>
       <c r="L217" s="13" t="n">
         <v>20</v>
       </c>
       <c r="M217" s="13" t="n">
-        <v>820</v>
+        <v>740</v>
       </c>
       <c r="N217" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O217" s="11" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="P217" s="11" t="n"/>
       <c r="Q217" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #85)</t>
         </is>
       </c>
     </row>
@@ -35083,7 +35294,7 @@
         </is>
       </c>
       <c r="I219" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J219" s="11" t="n">
         <v>52</v>
@@ -35102,7 +35313,7 @@
       <c r="P219" s="11" t="n"/>
       <c r="Q219" s="12" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -35167,7 +35378,7 @@
       <c r="P220" s="7" t="n"/>
       <c r="Q220" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55, Partner: LETZBLRIP7026684292)</t>
+          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55)</t>
         </is>
       </c>
     </row>
@@ -35215,24 +35426,24 @@
         <v>55</v>
       </c>
       <c r="K221" s="13" t="n">
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="L221" s="13" t="n">
         <v>20</v>
       </c>
       <c r="M221" s="13" t="n">
-        <v>820</v>
+        <v>780</v>
       </c>
       <c r="N221" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O221" s="11" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="P221" s="11" t="n"/>
       <c r="Q221" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #83)</t>
         </is>
       </c>
     </row>
@@ -35358,7 +35569,7 @@
       <c r="P223" s="11" t="n"/>
       <c r="Q223" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #68, Partner: LETZBLRIP7025077468)</t>
+          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #68)</t>
         </is>
       </c>
     </row>
@@ -35406,24 +35617,24 @@
         <v>58</v>
       </c>
       <c r="K224" s="9" t="n">
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="L224" s="9" t="n">
         <v>20</v>
       </c>
       <c r="M224" s="9" t="n">
-        <v>820</v>
+        <v>780</v>
       </c>
       <c r="N224" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O224" s="7" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="P224" s="7" t="n"/>
       <c r="Q224" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #83)</t>
         </is>
       </c>
     </row>
@@ -35541,7 +35752,7 @@
         <v>970</v>
       </c>
       <c r="N226" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O226" s="7" t="n"/>
       <c r="P226" s="7" t="n">
@@ -35591,7 +35802,7 @@
         </is>
       </c>
       <c r="I227" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J227" s="11" t="n">
         <v>3</v>
@@ -35610,7 +35821,7 @@
       <c r="P227" s="11" t="n"/>
       <c r="Q227" s="12" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -35789,7 +36000,7 @@
         <v>930</v>
       </c>
       <c r="N230" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O230" s="7" t="n"/>
       <c r="P230" s="7" t="n">
@@ -35862,7 +36073,7 @@
       <c r="P231" s="11" t="n"/>
       <c r="Q231" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -35927,7 +36138,7 @@
       <c r="P232" s="7" t="n"/>
       <c r="Q232" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -35992,7 +36203,7 @@
       <c r="P233" s="11" t="n"/>
       <c r="Q233" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #10, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #10)</t>
         </is>
       </c>
     </row>
@@ -36095,7 +36306,7 @@
         </is>
       </c>
       <c r="I235" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" s="11" t="n">
         <v>5</v>
@@ -36114,7 +36325,7 @@
       <c r="P235" s="11" t="n"/>
       <c r="Q235" s="12" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -36156,7 +36367,7 @@
         </is>
       </c>
       <c r="I236" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J236" s="7" t="n">
         <v>36</v>
@@ -36175,7 +36386,7 @@
       <c r="P236" s="7" t="n"/>
       <c r="Q236" s="8" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -36240,7 +36451,7 @@
       <c r="P237" s="11" t="n"/>
       <c r="Q237" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #77, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #77)</t>
         </is>
       </c>
     </row>
@@ -36305,7 +36516,7 @@
       <c r="P238" s="7" t="n"/>
       <c r="Q238" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -36362,15 +36573,15 @@
         <v>959</v>
       </c>
       <c r="N239" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O239" s="11" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P239" s="11" t="n"/>
       <c r="Q239" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -36435,7 +36646,7 @@
       <c r="P240" s="7" t="n"/>
       <c r="Q240" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #69, Partner: LETZBLRIP7025077468)</t>
+          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #69)</t>
         </is>
       </c>
     </row>
@@ -36491,16 +36702,12 @@
       <c r="M241" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N241" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O241" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N241" s="11" t="n"/>
+      <c r="O241" s="11" t="n"/>
       <c r="P241" s="11" t="n"/>
       <c r="Q241" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -36603,7 +36810,7 @@
         </is>
       </c>
       <c r="I243" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J243" s="11" t="n">
         <v>12</v>
@@ -36622,7 +36829,7 @@
       <c r="P243" s="11" t="n"/>
       <c r="Q243" s="12" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -36679,15 +36886,15 @@
         <v>1019</v>
       </c>
       <c r="N244" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O244" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P244" s="7" t="n"/>
       <c r="Q244" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #1, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #13)</t>
         </is>
       </c>
     </row>
@@ -36744,7 +36951,7 @@
         <v>980</v>
       </c>
       <c r="N245" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O245" s="11" t="n"/>
       <c r="P245" s="11" t="n">
@@ -36864,10 +37071,10 @@
         <v>970</v>
       </c>
       <c r="L247" s="13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M247" s="13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="N247" s="11" t="n">
         <v>10</v>
@@ -36878,7 +37085,7 @@
       <c r="P247" s="11" t="n"/>
       <c r="Q247" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #10: MUM_UBER_REDUCING, Slab #28, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #10: MUM_UBER_REDUCING, Slab #28)</t>
         </is>
       </c>
     </row>
@@ -36996,7 +37203,7 @@
         <v>970</v>
       </c>
       <c r="N249" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O249" s="11" t="n"/>
       <c r="P249" s="11" t="n">
@@ -37069,7 +37276,7 @@
       <c r="P250" s="7" t="n"/>
       <c r="Q250" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -37186,16 +37393,12 @@
       <c r="M252" s="9" t="n">
         <v>959</v>
       </c>
-      <c r="N252" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O252" s="7" t="n">
-        <v>35</v>
-      </c>
+      <c r="N252" s="7" t="n"/>
+      <c r="O252" s="7" t="n"/>
       <c r="P252" s="7" t="n"/>
       <c r="Q252" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -37237,7 +37440,7 @@
         </is>
       </c>
       <c r="I253" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J253" s="11" t="n">
         <v>10</v>
@@ -37256,7 +37459,7 @@
       <c r="P253" s="11" t="n"/>
       <c r="Q253" s="12" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -37321,7 +37524,7 @@
       <c r="P254" s="7" t="n"/>
       <c r="Q254" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #1, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #1)</t>
         </is>
       </c>
     </row>
@@ -37386,7 +37589,7 @@
       <c r="P255" s="11" t="n"/>
       <c r="Q255" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -37451,7 +37654,7 @@
       <c r="P256" s="7" t="n"/>
       <c r="Q256" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35)</t>
         </is>
       </c>
     </row>
@@ -37630,7 +37833,7 @@
         <v>930</v>
       </c>
       <c r="N259" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O259" s="11" t="n"/>
       <c r="P259" s="11" t="n">
@@ -37695,7 +37898,7 @@
         <v>970</v>
       </c>
       <c r="N260" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O260" s="7" t="n"/>
       <c r="P260" s="7" t="n">
@@ -37745,7 +37948,7 @@
         </is>
       </c>
       <c r="I261" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J261" s="11" t="n">
         <v>13</v>
@@ -37764,7 +37967,7 @@
       <c r="P261" s="11" t="n"/>
       <c r="Q261" s="12" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -37882,7 +38085,7 @@
         <v>970</v>
       </c>
       <c r="N263" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O263" s="11" t="n"/>
       <c r="P263" s="11" t="n">
@@ -38016,7 +38219,7 @@
       <c r="P265" s="11" t="n"/>
       <c r="Q265" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #68, Partner: LETZBLRIP7025077468)</t>
+          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #68)</t>
         </is>
       </c>
     </row>
@@ -38073,7 +38276,7 @@
         <v>980</v>
       </c>
       <c r="N266" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O266" s="7" t="n"/>
       <c r="P266" s="7" t="n">
@@ -38199,15 +38402,15 @@
         <v>1019</v>
       </c>
       <c r="N268" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O268" s="7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P268" s="7" t="n"/>
       <c r="Q268" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #1, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #13)</t>
         </is>
       </c>
     </row>
@@ -38455,7 +38658,7 @@
       <c r="P272" s="7" t="n"/>
       <c r="Q272" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -38520,7 +38723,7 @@
       <c r="P273" s="11" t="n"/>
       <c r="Q273" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #70, Partner: LETZBLRIP7025077468)</t>
+          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #70)</t>
         </is>
       </c>
     </row>
@@ -38568,24 +38771,24 @@
         <v>69</v>
       </c>
       <c r="K274" s="9" t="n">
-        <v>800</v>
+        <v>740</v>
       </c>
       <c r="L274" s="9" t="n">
         <v>20</v>
       </c>
       <c r="M274" s="9" t="n">
-        <v>820</v>
+        <v>760</v>
       </c>
       <c r="N274" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O274" s="7" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="P274" s="7" t="n"/>
       <c r="Q274" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #84)</t>
         </is>
       </c>
     </row>
@@ -38642,15 +38845,15 @@
         <v>959</v>
       </c>
       <c r="N275" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O275" s="11" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P275" s="11" t="n"/>
       <c r="Q275" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -38715,7 +38918,7 @@
       <c r="P276" s="7" t="n"/>
       <c r="Q276" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #64, Partner: LETZBLRIP8075280208)</t>
+          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #64)</t>
         </is>
       </c>
     </row>
@@ -38771,16 +38974,12 @@
       <c r="M277" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N277" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O277" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N277" s="11" t="n"/>
+      <c r="O277" s="11" t="n"/>
       <c r="P277" s="11" t="n"/>
       <c r="Q277" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -38845,7 +39044,7 @@
       <c r="P278" s="7" t="n"/>
       <c r="Q278" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35)</t>
         </is>
       </c>
     </row>
@@ -38902,15 +39101,15 @@
         <v>959</v>
       </c>
       <c r="N279" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O279" s="11" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P279" s="11" t="n"/>
       <c r="Q279" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -38975,7 +39174,7 @@
       <c r="P280" s="7" t="n"/>
       <c r="Q280" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #11, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #11)</t>
         </is>
       </c>
     </row>
@@ -39040,7 +39239,7 @@
       <c r="P281" s="11" t="n"/>
       <c r="Q281" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35)</t>
         </is>
       </c>
     </row>
@@ -39097,7 +39296,7 @@
         <v>970</v>
       </c>
       <c r="N282" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O282" s="7" t="n"/>
       <c r="P282" s="7" t="n">
@@ -39170,7 +39369,7 @@
       <c r="P283" s="11" t="n"/>
       <c r="Q283" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #80, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #80)</t>
         </is>
       </c>
     </row>
@@ -39287,16 +39486,12 @@
       <c r="M285" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N285" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O285" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N285" s="11" t="n"/>
+      <c r="O285" s="11" t="n"/>
       <c r="P285" s="11" t="n"/>
       <c r="Q285" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -39361,7 +39556,7 @@
       <c r="P286" s="7" t="n"/>
       <c r="Q286" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -39426,7 +39621,7 @@
       <c r="P287" s="11" t="n"/>
       <c r="Q287" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -39483,15 +39678,15 @@
         <v>959</v>
       </c>
       <c r="N288" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O288" s="7" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P288" s="7" t="n"/>
       <c r="Q288" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -39547,16 +39742,12 @@
       <c r="M289" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N289" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O289" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N289" s="11" t="n"/>
+      <c r="O289" s="11" t="n"/>
       <c r="P289" s="11" t="n"/>
       <c r="Q289" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -39682,7 +39873,7 @@
       <c r="P291" s="11" t="n"/>
       <c r="Q291" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #69, Partner: LETZBLRIP7025077468)</t>
+          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #69)</t>
         </is>
       </c>
     </row>
@@ -39747,7 +39938,7 @@
       <c r="P292" s="7" t="n"/>
       <c r="Q292" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -39804,7 +39995,7 @@
         <v>980</v>
       </c>
       <c r="N293" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O293" s="11" t="n"/>
       <c r="P293" s="11" t="n">
@@ -39854,7 +40045,7 @@
         </is>
       </c>
       <c r="I294" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J294" s="7" t="n">
         <v>1</v>
@@ -39873,7 +40064,7 @@
       <c r="P294" s="7" t="n"/>
       <c r="Q294" s="8" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -39930,7 +40121,7 @@
         <v>1000</v>
       </c>
       <c r="N295" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O295" s="11" t="n"/>
       <c r="P295" s="11" t="n">
@@ -40125,7 +40316,7 @@
       <c r="P298" s="7" t="n"/>
       <c r="Q298" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #41, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #41)</t>
         </is>
       </c>
     </row>
@@ -40190,7 +40381,7 @@
       <c r="P299" s="11" t="n"/>
       <c r="Q299" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #47, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #47)</t>
         </is>
       </c>
     </row>
@@ -40255,7 +40446,7 @@
       <c r="P300" s="7" t="n"/>
       <c r="Q300" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56, Partner: LETZBLRIP7356813050)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56)</t>
         </is>
       </c>
     </row>
@@ -40320,7 +40511,7 @@
       <c r="P301" s="11" t="n"/>
       <c r="Q301" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56, Partner: LETZBLRIP7356813050)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56)</t>
         </is>
       </c>
     </row>
@@ -40385,7 +40576,7 @@
       <c r="P302" s="7" t="n"/>
       <c r="Q302" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55, Partner: LETZBLRIP7026684292)</t>
+          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55)</t>
         </is>
       </c>
     </row>
@@ -40433,24 +40624,24 @@
         <v>60</v>
       </c>
       <c r="K303" s="13" t="n">
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="L303" s="13" t="n">
         <v>20</v>
       </c>
       <c r="M303" s="13" t="n">
-        <v>820</v>
+        <v>780</v>
       </c>
       <c r="N303" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O303" s="11" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="P303" s="11" t="n"/>
       <c r="Q303" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #83)</t>
         </is>
       </c>
     </row>
@@ -40567,16 +40758,12 @@
       <c r="M305" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N305" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O305" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N305" s="11" t="n"/>
+      <c r="O305" s="11" t="n"/>
       <c r="P305" s="11" t="n"/>
       <c r="Q305" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -40633,15 +40820,15 @@
         <v>959</v>
       </c>
       <c r="N306" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O306" s="7" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P306" s="7" t="n"/>
       <c r="Q306" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -40750,24 +40937,24 @@
         <v>80</v>
       </c>
       <c r="K308" s="9" t="n">
-        <v>800</v>
+        <v>720</v>
       </c>
       <c r="L308" s="9" t="n">
         <v>20</v>
       </c>
       <c r="M308" s="9" t="n">
-        <v>820</v>
+        <v>740</v>
       </c>
       <c r="N308" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O308" s="7" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="P308" s="7" t="n"/>
       <c r="Q308" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #85)</t>
         </is>
       </c>
     </row>
@@ -40832,7 +41019,7 @@
       <c r="P309" s="11" t="n"/>
       <c r="Q309" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -40958,7 +41145,7 @@
       <c r="P311" s="11" t="n"/>
       <c r="Q311" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #64, Partner: LETZBLRIP8075280208)</t>
+          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #64)</t>
         </is>
       </c>
     </row>
@@ -41015,15 +41202,15 @@
         <v>959</v>
       </c>
       <c r="N312" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O312" s="7" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P312" s="7" t="n"/>
       <c r="Q312" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -41088,7 +41275,7 @@
       <c r="P313" s="11" t="n"/>
       <c r="Q313" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #41, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #41)</t>
         </is>
       </c>
     </row>
@@ -41130,7 +41317,7 @@
         </is>
       </c>
       <c r="I314" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J314" s="7" t="n">
         <v>10</v>
@@ -41149,7 +41336,7 @@
       <c r="P314" s="7" t="n"/>
       <c r="Q314" s="8" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -41388,16 +41575,12 @@
       <c r="M318" s="9" t="n">
         <v>959</v>
       </c>
-      <c r="N318" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O318" s="7" t="n">
-        <v>35</v>
-      </c>
+      <c r="N318" s="7" t="n"/>
+      <c r="O318" s="7" t="n"/>
       <c r="P318" s="7" t="n"/>
       <c r="Q318" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -41445,24 +41628,24 @@
         <v>66</v>
       </c>
       <c r="K319" s="13" t="n">
-        <v>800</v>
+        <v>740</v>
       </c>
       <c r="L319" s="13" t="n">
         <v>20</v>
       </c>
       <c r="M319" s="13" t="n">
-        <v>820</v>
+        <v>760</v>
       </c>
       <c r="N319" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O319" s="11" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="P319" s="11" t="n"/>
       <c r="Q319" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #84)</t>
         </is>
       </c>
     </row>
@@ -41580,15 +41763,15 @@
         <v>959</v>
       </c>
       <c r="N321" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O321" s="11" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P321" s="11" t="n"/>
       <c r="Q321" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -41653,7 +41836,7 @@
       <c r="P322" s="7" t="n"/>
       <c r="Q322" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #15, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #15)</t>
         </is>
       </c>
     </row>
@@ -41710,7 +41893,7 @@
         <v>970</v>
       </c>
       <c r="N323" s="11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O323" s="11" t="n"/>
       <c r="P323" s="11" t="n">
@@ -41827,24 +42010,24 @@
         <v>59</v>
       </c>
       <c r="K325" s="13" t="n">
-        <v>889</v>
+        <v>989</v>
       </c>
       <c r="L325" s="13" t="n">
         <v>30</v>
       </c>
       <c r="M325" s="13" t="n">
-        <v>919</v>
+        <v>1019</v>
       </c>
       <c r="N325" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O325" s="11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="P325" s="11" t="n"/>
       <c r="Q325" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #2, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #13)</t>
         </is>
       </c>
     </row>
@@ -41901,7 +42084,7 @@
         <v>1080</v>
       </c>
       <c r="N326" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O326" s="7" t="n"/>
       <c r="P326" s="7" t="n">
@@ -42027,7 +42210,7 @@
         <v>930</v>
       </c>
       <c r="N328" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O328" s="7" t="n"/>
       <c r="P328" s="7" t="n">
@@ -42092,7 +42275,7 @@
         <v>970</v>
       </c>
       <c r="N329" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O329" s="11" t="n"/>
       <c r="P329" s="11" t="n">
@@ -42142,7 +42325,7 @@
         </is>
       </c>
       <c r="I330" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J330" s="7" t="n">
         <v>43</v>
@@ -42161,7 +42344,7 @@
       <c r="P330" s="7" t="n"/>
       <c r="Q330" s="8" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -42218,7 +42401,7 @@
         <v>980</v>
       </c>
       <c r="N331" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O331" s="11" t="n"/>
       <c r="P331" s="11" t="n">
@@ -42291,7 +42474,7 @@
       <c r="P332" s="7" t="n"/>
       <c r="Q332" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56, Partner: LETZBLRIP7356813050)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56)</t>
         </is>
       </c>
     </row>
@@ -42339,24 +42522,24 @@
         <v>70</v>
       </c>
       <c r="K333" s="13" t="n">
-        <v>800</v>
+        <v>740</v>
       </c>
       <c r="L333" s="13" t="n">
         <v>20</v>
       </c>
       <c r="M333" s="13" t="n">
-        <v>820</v>
+        <v>760</v>
       </c>
       <c r="N333" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O333" s="11" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="P333" s="11" t="n"/>
       <c r="Q333" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #84)</t>
         </is>
       </c>
     </row>
@@ -42421,7 +42604,7 @@
       <c r="P334" s="7" t="n"/>
       <c r="Q334" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #42, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #42)</t>
         </is>
       </c>
     </row>
@@ -42486,7 +42669,7 @@
       <c r="P335" s="11" t="n"/>
       <c r="Q335" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -42543,7 +42726,7 @@
         <v>1080</v>
       </c>
       <c r="N336" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O336" s="7" t="n"/>
       <c r="P336" s="7" t="n">
@@ -42677,7 +42860,7 @@
       <c r="P338" s="7" t="n"/>
       <c r="Q338" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -42742,7 +42925,7 @@
       <c r="P339" s="11" t="n"/>
       <c r="Q339" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -42807,7 +42990,7 @@
       <c r="P340" s="7" t="n"/>
       <c r="Q340" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -42872,7 +43055,7 @@
       <c r="P341" s="11" t="n"/>
       <c r="Q341" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -42937,7 +43120,7 @@
       <c r="P342" s="7" t="n"/>
       <c r="Q342" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #66, Partner: LETZBLRIP8075280208)</t>
+          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #66)</t>
         </is>
       </c>
     </row>
@@ -43002,7 +43185,7 @@
       <c r="P343" s="11" t="n"/>
       <c r="Q343" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #71, Partner: LETZBLRIP7025077468)</t>
+          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #71)</t>
         </is>
       </c>
     </row>
@@ -43067,7 +43250,7 @@
       <c r="P344" s="7" t="n"/>
       <c r="Q344" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #71, Partner: LETZBLRIP7025077468)</t>
+          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #71)</t>
         </is>
       </c>
     </row>
@@ -43185,7 +43368,7 @@
         <v>1080</v>
       </c>
       <c r="N346" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O346" s="7" t="n"/>
       <c r="P346" s="7" t="n">
@@ -43258,7 +43441,7 @@
       <c r="P347" s="11" t="n"/>
       <c r="Q347" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -43323,7 +43506,7 @@
       <c r="P348" s="7" t="n"/>
       <c r="Q348" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #77, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #77)</t>
         </is>
       </c>
     </row>
@@ -43380,15 +43563,15 @@
         <v>959</v>
       </c>
       <c r="N349" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O349" s="11" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P349" s="11" t="n"/>
       <c r="Q349" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -43436,24 +43619,24 @@
         <v>85</v>
       </c>
       <c r="K350" s="9" t="n">
-        <v>869</v>
+        <v>929</v>
       </c>
       <c r="L350" s="9" t="n">
         <v>30</v>
       </c>
       <c r="M350" s="9" t="n">
-        <v>899</v>
+        <v>959</v>
       </c>
       <c r="N350" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O350" s="7" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="P350" s="7" t="n"/>
       <c r="Q350" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #47, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35)</t>
         </is>
       </c>
     </row>
@@ -43518,7 +43701,7 @@
       <c r="P351" s="11" t="n"/>
       <c r="Q351" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -43575,7 +43758,7 @@
         <v>1080</v>
       </c>
       <c r="N352" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O352" s="7" t="n"/>
       <c r="P352" s="7" t="n">
@@ -43648,7 +43831,7 @@
       <c r="P353" s="11" t="n"/>
       <c r="Q353" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -43713,7 +43896,7 @@
       <c r="P354" s="7" t="n"/>
       <c r="Q354" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #66, Partner: LETZBLRIP8075280208)</t>
+          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #66)</t>
         </is>
       </c>
     </row>
@@ -43769,16 +43952,12 @@
       <c r="M355" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N355" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O355" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N355" s="11" t="n"/>
+      <c r="O355" s="11" t="n"/>
       <c r="P355" s="11" t="n"/>
       <c r="Q355" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -43834,16 +44013,12 @@
       <c r="M356" s="9" t="n">
         <v>959</v>
       </c>
-      <c r="N356" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O356" s="7" t="n">
-        <v>35</v>
-      </c>
+      <c r="N356" s="7" t="n"/>
+      <c r="O356" s="7" t="n"/>
       <c r="P356" s="7" t="n"/>
       <c r="Q356" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -43908,7 +44083,7 @@
       <c r="P357" s="11" t="n"/>
       <c r="Q357" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55, Partner: LETZBLRIP7026684292)</t>
+          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55)</t>
         </is>
       </c>
     </row>
@@ -43956,24 +44131,24 @@
         <v>71</v>
       </c>
       <c r="K358" s="9" t="n">
-        <v>800</v>
+        <v>740</v>
       </c>
       <c r="L358" s="9" t="n">
         <v>20</v>
       </c>
       <c r="M358" s="9" t="n">
-        <v>820</v>
+        <v>760</v>
       </c>
       <c r="N358" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O358" s="7" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="P358" s="7" t="n"/>
       <c r="Q358" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #84)</t>
         </is>
       </c>
     </row>
@@ -44082,24 +44257,24 @@
         <v>67</v>
       </c>
       <c r="K360" s="9" t="n">
-        <v>800</v>
+        <v>740</v>
       </c>
       <c r="L360" s="9" t="n">
         <v>20</v>
       </c>
       <c r="M360" s="9" t="n">
-        <v>820</v>
+        <v>760</v>
       </c>
       <c r="N360" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O360" s="7" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="P360" s="7" t="n"/>
       <c r="Q360" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #84)</t>
         </is>
       </c>
     </row>
@@ -44164,7 +44339,7 @@
       <c r="P361" s="11" t="n"/>
       <c r="Q361" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -44229,7 +44404,7 @@
       <c r="P362" s="7" t="n"/>
       <c r="Q362" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -44294,7 +44469,7 @@
       <c r="P363" s="11" t="n"/>
       <c r="Q363" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #65, Partner: LETZBLRIP8075280208)</t>
+          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #65)</t>
         </is>
       </c>
     </row>
@@ -44359,7 +44534,7 @@
       <c r="P364" s="7" t="n"/>
       <c r="Q364" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #65, Partner: LETZBLRIP8075280208)</t>
+          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #65)</t>
         </is>
       </c>
     </row>
@@ -44599,7 +44774,7 @@
         <v>1080</v>
       </c>
       <c r="N368" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O368" s="7" t="n"/>
       <c r="P368" s="7" t="n">
@@ -44855,7 +45030,7 @@
       <c r="P372" s="7" t="n"/>
       <c r="Q372" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -44912,7 +45087,7 @@
         <v>980</v>
       </c>
       <c r="N373" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O373" s="11" t="n"/>
       <c r="P373" s="11" t="n">
@@ -44977,7 +45152,7 @@
         <v>980</v>
       </c>
       <c r="N374" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O374" s="7" t="n"/>
       <c r="P374" s="7" t="n">
@@ -45042,7 +45217,7 @@
         <v>970</v>
       </c>
       <c r="N375" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O375" s="11" t="n"/>
       <c r="P375" s="11" t="n">
@@ -45098,24 +45273,24 @@
         <v>70</v>
       </c>
       <c r="K376" s="9" t="n">
-        <v>800</v>
+        <v>740</v>
       </c>
       <c r="L376" s="9" t="n">
         <v>20</v>
       </c>
       <c r="M376" s="9" t="n">
-        <v>820</v>
+        <v>760</v>
       </c>
       <c r="N376" s="7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O376" s="7" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="P376" s="7" t="n"/>
       <c r="Q376" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #84)</t>
         </is>
       </c>
     </row>
@@ -45241,7 +45416,7 @@
       <c r="P378" s="7" t="n"/>
       <c r="Q378" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #5, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #5)</t>
         </is>
       </c>
     </row>
@@ -45306,7 +45481,7 @@
       <c r="P379" s="11" t="n"/>
       <c r="Q379" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #46, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #46)</t>
         </is>
       </c>
     </row>
@@ -45432,7 +45607,7 @@
       <c r="P381" s="11" t="n"/>
       <c r="Q381" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -45497,7 +45672,7 @@
       <c r="P382" s="7" t="n"/>
       <c r="Q382" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #42, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #42)</t>
         </is>
       </c>
     </row>
@@ -45562,7 +45737,7 @@
       <c r="P383" s="11" t="n"/>
       <c r="Q383" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56, Partner: LETZBLRIP7356813050)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56)</t>
         </is>
       </c>
     </row>
@@ -45619,7 +45794,7 @@
         <v>1100</v>
       </c>
       <c r="N384" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="O384" s="7" t="n"/>
       <c r="P384" s="7" t="n">
@@ -45692,7 +45867,7 @@
       <c r="P385" s="11" t="n"/>
       <c r="Q385" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56, Partner: LETZBLRIP7356813050)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56)</t>
         </is>
       </c>
     </row>
@@ -45757,7 +45932,7 @@
       <c r="P386" s="7" t="n"/>
       <c r="Q386" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #47, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #47)</t>
         </is>
       </c>
     </row>
@@ -45814,7 +45989,7 @@
         <v>1080</v>
       </c>
       <c r="N387" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O387" s="11" t="n"/>
       <c r="P387" s="11" t="n">
@@ -45864,7 +46039,7 @@
         </is>
       </c>
       <c r="I388" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J388" s="7" t="n">
         <v>7</v>
@@ -45883,7 +46058,7 @@
       <c r="P388" s="7" t="n"/>
       <c r="Q388" s="8" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -45934,10 +46109,10 @@
         <v>970</v>
       </c>
       <c r="L389" s="13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M389" s="13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="N389" s="11" t="n">
         <v>10</v>
@@ -45948,7 +46123,7 @@
       <c r="P389" s="11" t="n"/>
       <c r="Q389" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #10: MUM_UBER_REDUCING, Slab #28, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #10: MUM_UBER_REDUCING, Slab #28)</t>
         </is>
       </c>
     </row>
@@ -46074,7 +46249,7 @@
       <c r="P391" s="11" t="n"/>
       <c r="Q391" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -46566,7 +46741,7 @@
       <c r="P399" s="11" t="n"/>
       <c r="Q399" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #45, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #45)</t>
         </is>
       </c>
     </row>
@@ -46631,7 +46806,7 @@
       <c r="P400" s="7" t="n"/>
       <c r="Q400" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #36, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #36)</t>
         </is>
       </c>
     </row>
@@ -46696,7 +46871,7 @@
       <c r="P401" s="11" t="n"/>
       <c r="Q401" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #71, Partner: LETZBLRIP7025077468)</t>
+          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #71)</t>
         </is>
       </c>
     </row>
@@ -46753,15 +46928,15 @@
         <v>959</v>
       </c>
       <c r="N402" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O402" s="7" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P402" s="7" t="n"/>
       <c r="Q402" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -46939,16 +47114,12 @@
       <c r="M405" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N405" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O405" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N405" s="11" t="n"/>
+      <c r="O405" s="11" t="n"/>
       <c r="P405" s="11" t="n"/>
       <c r="Q405" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -47005,7 +47176,7 @@
         <v>1080</v>
       </c>
       <c r="N406" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O406" s="7" t="n"/>
       <c r="P406" s="7" t="n">
@@ -47131,7 +47302,7 @@
         <v>980</v>
       </c>
       <c r="N408" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O408" s="7" t="n"/>
       <c r="P408" s="7" t="n">
@@ -47181,7 +47352,7 @@
         </is>
       </c>
       <c r="I409" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J409" s="11" t="n">
         <v>1</v>
@@ -47200,7 +47371,7 @@
       <c r="P409" s="11" t="n"/>
       <c r="Q409" s="12" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -47265,7 +47436,7 @@
       <c r="P410" s="7" t="n"/>
       <c r="Q410" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -47307,7 +47478,7 @@
         </is>
       </c>
       <c r="I411" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J411" s="11" t="n">
         <v>4</v>
@@ -47326,7 +47497,7 @@
       <c r="P411" s="11" t="n"/>
       <c r="Q411" s="12" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -47383,7 +47554,7 @@
         <v>980</v>
       </c>
       <c r="N412" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O412" s="7" t="n"/>
       <c r="P412" s="7" t="n">
@@ -47509,7 +47680,7 @@
         <v>980</v>
       </c>
       <c r="N414" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O414" s="7" t="n"/>
       <c r="P414" s="7" t="n">
@@ -47643,7 +47814,7 @@
       <c r="P416" s="7" t="n"/>
       <c r="Q416" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #43, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #43)</t>
         </is>
       </c>
     </row>
@@ -47708,7 +47879,7 @@
       <c r="P417" s="11" t="n"/>
       <c r="Q417" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -47773,7 +47944,7 @@
       <c r="P418" s="7" t="n"/>
       <c r="Q418" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -47838,7 +48009,7 @@
       <c r="P419" s="11" t="n"/>
       <c r="Q419" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #42, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #42)</t>
         </is>
       </c>
     </row>
@@ -48025,7 +48196,7 @@
       <c r="P422" s="7" t="n"/>
       <c r="Q422" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #65, Partner: LETZBLRIP8075280208)</t>
+          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #65)</t>
         </is>
       </c>
     </row>
@@ -48090,7 +48261,7 @@
       <c r="P423" s="11" t="n"/>
       <c r="Q423" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56, Partner: LETZBLRIP7356813050)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #56)</t>
         </is>
       </c>
     </row>
@@ -48147,7 +48318,7 @@
         <v>1080</v>
       </c>
       <c r="N424" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O424" s="7" t="n"/>
       <c r="P424" s="7" t="n">
@@ -48220,7 +48391,7 @@
       <c r="P425" s="11" t="n"/>
       <c r="Q425" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -48277,7 +48448,7 @@
         <v>1080</v>
       </c>
       <c r="N426" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O426" s="7" t="n"/>
       <c r="P426" s="7" t="n">
@@ -48472,7 +48643,7 @@
       <c r="P429" s="11" t="n"/>
       <c r="Q429" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #61, Partner: LETZBLRIP7306249935)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #61)</t>
         </is>
       </c>
     </row>
@@ -48537,7 +48708,7 @@
       <c r="P430" s="7" t="n"/>
       <c r="Q430" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #42, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #42)</t>
         </is>
       </c>
     </row>
@@ -48602,7 +48773,7 @@
       <c r="P431" s="11" t="n"/>
       <c r="Q431" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -48667,7 +48838,7 @@
       <c r="P432" s="7" t="n"/>
       <c r="Q432" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #64, Partner: LETZBLRIP8075280208)</t>
+          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #64)</t>
         </is>
       </c>
     </row>
@@ -48709,7 +48880,7 @@
         </is>
       </c>
       <c r="I433" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J433" s="11" t="n">
         <v>25</v>
@@ -48728,7 +48899,7 @@
       <c r="P433" s="11" t="n"/>
       <c r="Q433" s="12" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -48793,7 +48964,7 @@
       <c r="P434" s="7" t="n"/>
       <c r="Q434" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -48858,7 +49029,7 @@
       <c r="P435" s="11" t="n"/>
       <c r="Q435" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #71, Partner: LETZBLRIP7025077468)</t>
+          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #71)</t>
         </is>
       </c>
     </row>
@@ -48923,7 +49094,7 @@
       <c r="P436" s="7" t="n"/>
       <c r="Q436" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -49041,15 +49212,15 @@
         <v>959</v>
       </c>
       <c r="N438" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O438" s="7" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P438" s="7" t="n"/>
       <c r="Q438" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -49091,7 +49262,7 @@
         </is>
       </c>
       <c r="I439" s="14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J439" s="11" t="n">
         <v>3</v>
@@ -49110,7 +49281,7 @@
       <c r="P439" s="11" t="n"/>
       <c r="Q439" s="12" t="inlineStr">
         <is>
-          <t>Unallocated / Yard</t>
+          <t>Non-billable status: Active</t>
         </is>
       </c>
     </row>
@@ -49167,15 +49338,15 @@
         <v>959</v>
       </c>
       <c r="N440" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O440" s="7" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P440" s="7" t="n"/>
       <c r="Q440" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -49231,16 +49402,12 @@
       <c r="M441" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N441" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O441" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N441" s="11" t="n"/>
+      <c r="O441" s="11" t="n"/>
       <c r="P441" s="11" t="n"/>
       <c r="Q441" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -49366,7 +49533,7 @@
       <c r="P443" s="11" t="n"/>
       <c r="Q443" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #46, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #46)</t>
         </is>
       </c>
     </row>
@@ -49423,7 +49590,7 @@
         <v>1000</v>
       </c>
       <c r="N444" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O444" s="7" t="n"/>
       <c r="P444" s="7" t="n">
@@ -49549,7 +49716,7 @@
         <v>1080</v>
       </c>
       <c r="N446" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O446" s="7" t="n"/>
       <c r="P446" s="7" t="n">
@@ -49614,7 +49781,7 @@
         <v>970</v>
       </c>
       <c r="N447" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O447" s="11" t="n"/>
       <c r="P447" s="11" t="n">
@@ -49740,15 +49907,15 @@
         <v>959</v>
       </c>
       <c r="N449" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O449" s="11" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P449" s="11" t="n"/>
       <c r="Q449" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -49813,7 +49980,7 @@
       <c r="P450" s="7" t="n"/>
       <c r="Q450" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #60, Partner: LETZBLRIP7306249935)</t>
+          <t>Priority 3: Dynamic Slab (Plan #16: BLR_OP_RISHAN_SARBAS, Slab #60)</t>
         </is>
       </c>
     </row>
@@ -49878,7 +50045,7 @@
       <c r="P451" s="11" t="n"/>
       <c r="Q451" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -49926,24 +50093,24 @@
         <v>60</v>
       </c>
       <c r="K452" s="9" t="n">
-        <v>849</v>
+        <v>989</v>
       </c>
       <c r="L452" s="9" t="n">
         <v>30</v>
       </c>
       <c r="M452" s="9" t="n">
-        <v>879</v>
+        <v>1019</v>
       </c>
       <c r="N452" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O452" s="7" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="P452" s="7" t="n"/>
       <c r="Q452" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #3, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #13)</t>
         </is>
       </c>
     </row>
@@ -50008,7 +50175,7 @@
       <c r="P453" s="11" t="n"/>
       <c r="Q453" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #40)</t>
         </is>
       </c>
     </row>
@@ -50073,7 +50240,7 @@
       <c r="P454" s="7" t="n"/>
       <c r="Q454" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #77, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #77)</t>
         </is>
       </c>
     </row>
@@ -50130,7 +50297,7 @@
         <v>980</v>
       </c>
       <c r="N455" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O455" s="11" t="n"/>
       <c r="P455" s="11" t="n">
@@ -50317,15 +50484,15 @@
         <v>959</v>
       </c>
       <c r="N458" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O458" s="7" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P458" s="7" t="n"/>
       <c r="Q458" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -50390,7 +50557,7 @@
       <c r="P459" s="11" t="n"/>
       <c r="Q459" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -50455,7 +50622,7 @@
       <c r="P460" s="7" t="n"/>
       <c r="Q460" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55, Partner: LETZBLRIP7026684292)</t>
+          <t>Priority 3: Dynamic Slab (Plan #15: BLR_OP_SUBHAN, Slab #55)</t>
         </is>
       </c>
     </row>
@@ -50512,15 +50679,15 @@
         <v>959</v>
       </c>
       <c r="N461" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O461" s="11" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="P461" s="11" t="n"/>
       <c r="Q461" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #3: BLR_UBER_TBS, Slab #44)</t>
         </is>
       </c>
     </row>
@@ -50646,7 +50813,7 @@
       <c r="P463" s="11" t="n"/>
       <c r="Q463" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #71, Partner: LETZBLRIP7025077468)</t>
+          <t>Priority 3: Dynamic Slab (Plan #14: BLR_OP_HAMZA, Slab #71)</t>
         </is>
       </c>
     </row>
@@ -50772,7 +50939,7 @@
       <c r="P465" s="11" t="n"/>
       <c r="Q465" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #77, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #77)</t>
         </is>
       </c>
     </row>
@@ -50829,7 +50996,7 @@
         <v>930</v>
       </c>
       <c r="N466" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O466" s="7" t="n"/>
       <c r="P466" s="7" t="n">
@@ -50955,7 +51122,7 @@
         <v>970</v>
       </c>
       <c r="N468" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O468" s="7" t="n"/>
       <c r="P468" s="7" t="n">
@@ -51028,7 +51195,7 @@
       <c r="P469" s="11" t="n"/>
       <c r="Q469" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #1, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #1)</t>
         </is>
       </c>
     </row>
@@ -51076,24 +51243,24 @@
         <v>96</v>
       </c>
       <c r="K470" s="9" t="n">
-        <v>679</v>
+        <v>799</v>
       </c>
       <c r="L470" s="9" t="n">
         <v>30</v>
       </c>
       <c r="M470" s="9" t="n">
-        <v>709</v>
+        <v>829</v>
       </c>
       <c r="N470" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O470" s="7" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P470" s="7" t="n"/>
       <c r="Q470" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #7: HYD_UBER_EBS, Slab #14, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #4)</t>
         </is>
       </c>
     </row>
@@ -51158,7 +51325,7 @@
       <c r="P471" s="11" t="n"/>
       <c r="Q471" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #2, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #6: HYD_UBER_TBS, Slab #2)</t>
         </is>
       </c>
     </row>
@@ -51275,16 +51442,12 @@
       <c r="M473" s="13" t="n">
         <v>959</v>
       </c>
-      <c r="N473" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O473" s="11" t="n">
-        <v>35</v>
-      </c>
+      <c r="N473" s="11" t="n"/>
+      <c r="O473" s="11" t="n"/>
       <c r="P473" s="11" t="n"/>
       <c r="Q473" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #1: BLR_MASTER_IND, Slab #35, Partner: ALL)</t>
+          <t>Priority 4: Model Baseline (Baseline #2: WagonR)</t>
         </is>
       </c>
     </row>
@@ -51393,24 +51556,24 @@
         <v>55</v>
       </c>
       <c r="K475" s="13" t="n">
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="L475" s="13" t="n">
         <v>20</v>
       </c>
       <c r="M475" s="13" t="n">
-        <v>820</v>
+        <v>780</v>
       </c>
       <c r="N475" s="11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O475" s="11" t="n">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="P475" s="11" t="n"/>
       <c r="Q475" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #17: BLR_OP_RISHAD_TBS, Slab #83)</t>
         </is>
       </c>
     </row>
@@ -51658,7 +51821,7 @@
       <c r="P479" s="11" t="n"/>
       <c r="Q479" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -51776,7 +51939,7 @@
         <v>980</v>
       </c>
       <c r="N481" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O481" s="11" t="n"/>
       <c r="P481" s="11" t="n">
@@ -51841,7 +52004,7 @@
         <v>970</v>
       </c>
       <c r="N482" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O482" s="7" t="n"/>
       <c r="P482" s="7" t="n">
@@ -51906,7 +52069,7 @@
         <v>970</v>
       </c>
       <c r="N483" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O483" s="11" t="n"/>
       <c r="P483" s="11" t="n">
@@ -51979,7 +52142,7 @@
       <c r="P484" s="7" t="n"/>
       <c r="Q484" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #64, Partner: LETZBLRIP8075280208)</t>
+          <t>Priority 3: Dynamic Slab (Plan #19: BLR_OP_RAMEES, Slab #64)</t>
         </is>
       </c>
     </row>
@@ -52044,7 +52207,7 @@
       <c r="P485" s="11" t="n"/>
       <c r="Q485" s="12" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76, Partner: LETZBLRIP9656907001)</t>
+          <t>Priority 3: Dynamic Slab (Plan #18: BLR_OP_RISHAD_EBS, Slab #76)</t>
         </is>
       </c>
     </row>
@@ -52162,7 +52325,7 @@
         <v>970</v>
       </c>
       <c r="N487" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O487" s="11" t="n"/>
       <c r="P487" s="11" t="n">
@@ -52471,7 +52634,7 @@
         <v>980</v>
       </c>
       <c r="N492" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O492" s="7" t="n"/>
       <c r="P492" s="7" t="n">
@@ -52605,7 +52768,7 @@
       <c r="P494" s="7" t="n"/>
       <c r="Q494" s="8" t="inlineStr">
         <is>
-          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #41, Partner: ALL)</t>
+          <t>Priority 3: Dynamic Slab (Plan #2: BLR_MASTER_OP, Slab #41)</t>
         </is>
       </c>
     </row>
@@ -52662,7 +52825,7 @@
         <v>970</v>
       </c>
       <c r="N495" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O495" s="11" t="n"/>
       <c r="P495" s="11" t="n">
@@ -52910,7 +53073,7 @@
         <v>1100</v>
       </c>
       <c r="N499" s="11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O499" s="11" t="n"/>
       <c r="P499" s="11" t="n">
@@ -52975,7 +53138,7 @@
         <v>1100</v>
       </c>
       <c r="N500" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O500" s="7" t="n"/>
       <c r="P500" s="7" t="n">
